--- a/data/UOL_Internship_Source_Records_20261027.xlsx
+++ b/data/UOL_Internship_Source_Records_20261027.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Internship Source Records" sheetId="1" r:id="Rfdd7217d5bc14b39"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Internship Source Records" sheetId="1" r:id="R59e3483e2f2e4a51"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -13,18 +13,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="3">
+  <x:fonts count="2">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
     </x:font>
     <x:font>
-      <x:sz val="11"/>
-      <x:color rgb="FFFFFFFF"/>
-      <x:name val="Carlito"/>
-    </x:font>
-    <x:font>
-      <x:b/>
       <x:sz val="11"/>
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Carlito"/>
@@ -39,7 +33,7 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FF173B56"/>
+        <x:fgColor rgb="FF16385A"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -50,14 +44,12 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="7">
+  <x:cellXfs count="5">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -259,65 +251,57 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="16" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="34" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="34" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="42" hidden="0" customWidth="1"/>
-    <x:col min="17" max="17" width="60" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="12" hidden="0" customWidth="1"/>
-  </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="32" customHeight="1">
-      <x:c r="A1" s="6" t="str">
+    <x:row r="1">
+      <x:c r="A1" s="4" t="str">
         <x:v>Ref #</x:v>
       </x:c>
-      <x:c r="B1" s="6" t="str">
+      <x:c r="B1" s="4" t="str">
         <x:v>Submitted By</x:v>
       </x:c>
-      <x:c r="C1" s="6" t="str">
+      <x:c r="C1" s="4" t="str">
         <x:v>Submission Status</x:v>
       </x:c>
-      <x:c r="D1" s="6" t="str">
+      <x:c r="D1" s="4" t="str">
         <x:v>Submission Date</x:v>
       </x:c>
-      <x:c r="E1" s="6" t="str">
+      <x:c r="E1" s="4" t="str">
         <x:v>Reporting Month</x:v>
       </x:c>
-      <x:c r="F1" s="6" t="str">
+      <x:c r="F1" s="4" t="str">
         <x:v>Campus</x:v>
       </x:c>
-      <x:c r="G1" s="6" t="str">
+      <x:c r="G1" s="4" t="str">
         <x:v>Faculty</x:v>
       </x:c>
-      <x:c r="H1" s="6" t="str">
+      <x:c r="H1" s="4" t="str">
         <x:v>Department</x:v>
       </x:c>
-      <x:c r="I1" s="6" t="str">
+      <x:c r="I1" s="4" t="str">
         <x:v>Focal Person</x:v>
       </x:c>
-      <x:c r="J1" s="6" t="str">
+      <x:c r="J1" s="4" t="str">
         <x:v>Designation</x:v>
       </x:c>
-      <x:c r="K1" s="6" t="str">
+      <x:c r="K1" s="4" t="str">
         <x:v>Separated Activity Type</x:v>
       </x:c>
-      <x:c r="L1" s="6" t="str">
+      <x:c r="L1" s="4" t="str">
         <x:v>Original Activity Type</x:v>
       </x:c>
-      <x:c r="M1" s="6" t="str">
+      <x:c r="M1" s="4" t="str">
         <x:v>How Many</x:v>
       </x:c>
-      <x:c r="N1" s="6" t="str">
+      <x:c r="N1" s="4" t="str">
         <x:v>Organization / Activity Title</x:v>
       </x:c>
-      <x:c r="O1" s="6" t="str">
+      <x:c r="O1" s="4" t="str">
         <x:v>Planned</x:v>
       </x:c>
-      <x:c r="P1" s="6" t="str">
+      <x:c r="P1" s="4" t="str">
         <x:v>Scheduled</x:v>
       </x:c>
-      <x:c r="Q1" s="6" t="str">
+      <x:c r="Q1" s="4" t="str">
         <x:v>Remarks / Result</x:v>
       </x:c>
     </x:row>
@@ -414,9 +398,7 @@
       <x:c r="M3" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="N3" t="str">
-        <x:v>...</x:v>
-      </x:c>
+      <x:c r="N3" t="str"/>
       <x:c r="O3" t="str">
         <x:v>No</x:v>
       </x:c>
@@ -440,7 +422,7 @@
       <x:c r="D4" t="str">
         <x:v>22 July 2026</x:v>
       </x:c>
-      <x:c r="E4"/>
+      <x:c r="E4" t="str"/>
       <x:c r="F4" t="str">
         <x:v>Lahore Campus</x:v>
       </x:c>
@@ -465,10 +447,10 @@
       <x:c r="M4" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="N4"/>
-      <x:c r="O4"/>
-      <x:c r="P4"/>
-      <x:c r="Q4"/>
+      <x:c r="N4" t="str"/>
+      <x:c r="O4" t="str"/>
+      <x:c r="P4" t="str"/>
+      <x:c r="Q4" t="str"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5" t="str">
@@ -801,7 +783,7 @@
       <x:c r="D11" t="str">
         <x:v>17 July 2026</x:v>
       </x:c>
-      <x:c r="E11"/>
+      <x:c r="E11" t="str"/>
       <x:c r="F11" t="str">
         <x:v>Lahore Campus</x:v>
       </x:c>
@@ -814,7 +796,7 @@
       <x:c r="I11" t="str">
         <x:v>Foc Dot Lhr</x:v>
       </x:c>
-      <x:c r="J11"/>
+      <x:c r="J11" t="str"/>
       <x:c r="K11" t="str">
         <x:v>Internship / Placement</x:v>
       </x:c>
@@ -830,8 +812,8 @@
       <x:c r="O11" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="P11"/>
-      <x:c r="Q11"/>
+      <x:c r="P11" t="str"/>
+      <x:c r="Q11" t="str"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12" t="str">
@@ -846,7 +828,7 @@
       <x:c r="D12" t="str">
         <x:v>17 July 2026</x:v>
       </x:c>
-      <x:c r="E12"/>
+      <x:c r="E12" t="str"/>
       <x:c r="F12" t="str">
         <x:v>Lahore Campus</x:v>
       </x:c>
@@ -859,7 +841,7 @@
       <x:c r="I12" t="str">
         <x:v>Foc Dot Lhr</x:v>
       </x:c>
-      <x:c r="J12"/>
+      <x:c r="J12" t="str"/>
       <x:c r="K12" t="str">
         <x:v>Internship / Placement</x:v>
       </x:c>
@@ -875,8 +857,8 @@
       <x:c r="O12" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="P12"/>
-      <x:c r="Q12"/>
+      <x:c r="P12" t="str"/>
+      <x:c r="Q12" t="str"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" t="str">
@@ -891,7 +873,7 @@
       <x:c r="D13" t="str">
         <x:v>17 July 2026</x:v>
       </x:c>
-      <x:c r="E13"/>
+      <x:c r="E13" t="str"/>
       <x:c r="F13" t="str">
         <x:v>Lahore Campus</x:v>
       </x:c>
@@ -904,7 +886,7 @@
       <x:c r="I13" t="str">
         <x:v>Foc Dot Lhr</x:v>
       </x:c>
-      <x:c r="J13"/>
+      <x:c r="J13" t="str"/>
       <x:c r="K13" t="str">
         <x:v>Internship / Placement</x:v>
       </x:c>
@@ -920,8 +902,8 @@
       <x:c r="O13" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="P13"/>
-      <x:c r="Q13"/>
+      <x:c r="P13" t="str"/>
+      <x:c r="Q13" t="str"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" t="str">
@@ -936,7 +918,7 @@
       <x:c r="D14" t="str">
         <x:v>17 July 2026</x:v>
       </x:c>
-      <x:c r="E14"/>
+      <x:c r="E14" t="str"/>
       <x:c r="F14" t="str">
         <x:v>Lahore Campus</x:v>
       </x:c>
@@ -949,7 +931,7 @@
       <x:c r="I14" t="str">
         <x:v>Foc Dot Lhr</x:v>
       </x:c>
-      <x:c r="J14"/>
+      <x:c r="J14" t="str"/>
       <x:c r="K14" t="str">
         <x:v>Internship / Placement</x:v>
       </x:c>
@@ -965,8 +947,8 @@
       <x:c r="O14" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="P14"/>
-      <x:c r="Q14"/>
+      <x:c r="P14" t="str"/>
+      <x:c r="Q14" t="str"/>
     </x:row>
     <x:row r="15">
       <x:c r="A15" t="str">
@@ -981,7 +963,7 @@
       <x:c r="D15" t="str">
         <x:v>17 July 2026</x:v>
       </x:c>
-      <x:c r="E15"/>
+      <x:c r="E15" t="str"/>
       <x:c r="F15" t="str">
         <x:v>Lahore Campus</x:v>
       </x:c>
@@ -994,7 +976,7 @@
       <x:c r="I15" t="str">
         <x:v>Foc Dot Lhr</x:v>
       </x:c>
-      <x:c r="J15"/>
+      <x:c r="J15" t="str"/>
       <x:c r="K15" t="str">
         <x:v>Internship / Placement</x:v>
       </x:c>
@@ -1010,8 +992,8 @@
       <x:c r="O15" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="P15"/>
-      <x:c r="Q15"/>
+      <x:c r="P15" t="str"/>
+      <x:c r="Q15" t="str"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16" t="str">
@@ -1026,7 +1008,7 @@
       <x:c r="D16" t="str">
         <x:v>17 July 2026</x:v>
       </x:c>
-      <x:c r="E16"/>
+      <x:c r="E16" t="str"/>
       <x:c r="F16" t="str">
         <x:v>Lahore Campus</x:v>
       </x:c>
@@ -1039,7 +1021,7 @@
       <x:c r="I16" t="str">
         <x:v>Foc Dot Lhr</x:v>
       </x:c>
-      <x:c r="J16"/>
+      <x:c r="J16" t="str"/>
       <x:c r="K16" t="str">
         <x:v>Internship / Placement</x:v>
       </x:c>
@@ -1055,8 +1037,8 @@
       <x:c r="O16" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="P16"/>
-      <x:c r="Q16"/>
+      <x:c r="P16" t="str"/>
+      <x:c r="Q16" t="str"/>
     </x:row>
     <x:row r="17">
       <x:c r="A17" t="str">
@@ -1071,7 +1053,7 @@
       <x:c r="D17" t="str">
         <x:v>17 July 2026</x:v>
       </x:c>
-      <x:c r="E17"/>
+      <x:c r="E17" t="str"/>
       <x:c r="F17" t="str">
         <x:v>Lahore Campus</x:v>
       </x:c>
@@ -1084,7 +1066,7 @@
       <x:c r="I17" t="str">
         <x:v>Foc Dot Lhr</x:v>
       </x:c>
-      <x:c r="J17"/>
+      <x:c r="J17" t="str"/>
       <x:c r="K17" t="str">
         <x:v>Internship / Placement</x:v>
       </x:c>
@@ -1100,8 +1082,8 @@
       <x:c r="O17" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="P17"/>
-      <x:c r="Q17"/>
+      <x:c r="P17" t="str"/>
+      <x:c r="Q17" t="str"/>
     </x:row>
     <x:row r="18">
       <x:c r="A18" t="str">
@@ -1116,7 +1098,7 @@
       <x:c r="D18" t="str">
         <x:v>17 July 2026</x:v>
       </x:c>
-      <x:c r="E18"/>
+      <x:c r="E18" t="str"/>
       <x:c r="F18" t="str">
         <x:v>Lahore Campus</x:v>
       </x:c>
@@ -1129,7 +1111,7 @@
       <x:c r="I18" t="str">
         <x:v>Foc Dot Lhr</x:v>
       </x:c>
-      <x:c r="J18"/>
+      <x:c r="J18" t="str"/>
       <x:c r="K18" t="str">
         <x:v>Internship / Placement</x:v>
       </x:c>
@@ -1145,8 +1127,8 @@
       <x:c r="O18" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="P18"/>
-      <x:c r="Q18"/>
+      <x:c r="P18" t="str"/>
+      <x:c r="Q18" t="str"/>
     </x:row>
     <x:row r="19">
       <x:c r="A19" t="str">
@@ -1161,7 +1143,7 @@
       <x:c r="D19" t="str">
         <x:v>17 July 2026</x:v>
       </x:c>
-      <x:c r="E19"/>
+      <x:c r="E19" t="str"/>
       <x:c r="F19" t="str">
         <x:v>Lahore Campus</x:v>
       </x:c>
@@ -1174,7 +1156,7 @@
       <x:c r="I19" t="str">
         <x:v>Foc Dot Lhr</x:v>
       </x:c>
-      <x:c r="J19"/>
+      <x:c r="J19" t="str"/>
       <x:c r="K19" t="str">
         <x:v>Internship / Placement</x:v>
       </x:c>
@@ -1190,8 +1172,8 @@
       <x:c r="O19" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="P19"/>
-      <x:c r="Q19"/>
+      <x:c r="P19" t="str"/>
+      <x:c r="Q19" t="str"/>
     </x:row>
     <x:row r="20">
       <x:c r="A20" t="str">
@@ -1206,7 +1188,7 @@
       <x:c r="D20" t="str">
         <x:v>17 July 2026</x:v>
       </x:c>
-      <x:c r="E20"/>
+      <x:c r="E20" t="str"/>
       <x:c r="F20" t="str">
         <x:v>Lahore Campus</x:v>
       </x:c>
@@ -1219,7 +1201,7 @@
       <x:c r="I20" t="str">
         <x:v>Foc Dot Lhr</x:v>
       </x:c>
-      <x:c r="J20"/>
+      <x:c r="J20" t="str"/>
       <x:c r="K20" t="str">
         <x:v>Internship / Placement</x:v>
       </x:c>
@@ -1235,8 +1217,8 @@
       <x:c r="O20" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="P20"/>
-      <x:c r="Q20"/>
+      <x:c r="P20" t="str"/>
+      <x:c r="Q20" t="str"/>
     </x:row>
     <x:row r="21">
       <x:c r="A21" t="str">
@@ -1251,7 +1233,7 @@
       <x:c r="D21" t="str">
         <x:v>17 July 2026</x:v>
       </x:c>
-      <x:c r="E21"/>
+      <x:c r="E21" t="str"/>
       <x:c r="F21" t="str">
         <x:v>Lahore Campus</x:v>
       </x:c>
@@ -1264,7 +1246,7 @@
       <x:c r="I21" t="str">
         <x:v>Foc Dot Lhr</x:v>
       </x:c>
-      <x:c r="J21"/>
+      <x:c r="J21" t="str"/>
       <x:c r="K21" t="str">
         <x:v>Internship / Placement</x:v>
       </x:c>
@@ -1280,8 +1262,8 @@
       <x:c r="O21" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="P21"/>
-      <x:c r="Q21"/>
+      <x:c r="P21" t="str"/>
+      <x:c r="Q21" t="str"/>
     </x:row>
     <x:row r="22">
       <x:c r="A22" t="str">
@@ -1296,7 +1278,7 @@
       <x:c r="D22" t="str">
         <x:v>17 July 2026</x:v>
       </x:c>
-      <x:c r="E22"/>
+      <x:c r="E22" t="str"/>
       <x:c r="F22" t="str">
         <x:v>Lahore Campus</x:v>
       </x:c>
@@ -1309,7 +1291,7 @@
       <x:c r="I22" t="str">
         <x:v>Foc Dot Lhr</x:v>
       </x:c>
-      <x:c r="J22"/>
+      <x:c r="J22" t="str"/>
       <x:c r="K22" t="str">
         <x:v>Internship / Placement</x:v>
       </x:c>
@@ -1325,8 +1307,8 @@
       <x:c r="O22" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="P22"/>
-      <x:c r="Q22"/>
+      <x:c r="P22" t="str"/>
+      <x:c r="Q22" t="str"/>
     </x:row>
     <x:row r="23">
       <x:c r="A23" t="str">
@@ -1341,7 +1323,7 @@
       <x:c r="D23" t="str">
         <x:v>17 July 2026</x:v>
       </x:c>
-      <x:c r="E23"/>
+      <x:c r="E23" t="str"/>
       <x:c r="F23" t="str">
         <x:v>Lahore Campus</x:v>
       </x:c>
@@ -1354,7 +1336,7 @@
       <x:c r="I23" t="str">
         <x:v>Foc Dot Lhr</x:v>
       </x:c>
-      <x:c r="J23"/>
+      <x:c r="J23" t="str"/>
       <x:c r="K23" t="str">
         <x:v>Internship / Placement</x:v>
       </x:c>
@@ -1370,8 +1352,8 @@
       <x:c r="O23" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="P23"/>
-      <x:c r="Q23"/>
+      <x:c r="P23" t="str"/>
+      <x:c r="Q23" t="str"/>
     </x:row>
     <x:row r="24">
       <x:c r="A24" t="str">
@@ -1386,7 +1368,7 @@
       <x:c r="D24" t="str">
         <x:v>17 July 2026</x:v>
       </x:c>
-      <x:c r="E24"/>
+      <x:c r="E24" t="str"/>
       <x:c r="F24" t="str">
         <x:v>Lahore Campus</x:v>
       </x:c>
@@ -1399,7 +1381,7 @@
       <x:c r="I24" t="str">
         <x:v>Foc Dot Lhr</x:v>
       </x:c>
-      <x:c r="J24"/>
+      <x:c r="J24" t="str"/>
       <x:c r="K24" t="str">
         <x:v>Internship / Placement</x:v>
       </x:c>
@@ -1415,8 +1397,8 @@
       <x:c r="O24" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="P24"/>
-      <x:c r="Q24"/>
+      <x:c r="P24" t="str"/>
+      <x:c r="Q24" t="str"/>
     </x:row>
     <x:row r="25">
       <x:c r="A25" t="str">
@@ -1431,7 +1413,7 @@
       <x:c r="D25" t="str">
         <x:v>17 July 2026</x:v>
       </x:c>
-      <x:c r="E25"/>
+      <x:c r="E25" t="str"/>
       <x:c r="F25" t="str">
         <x:v>Lahore Campus</x:v>
       </x:c>
@@ -1444,7 +1426,7 @@
       <x:c r="I25" t="str">
         <x:v>Foc Dot Lhr</x:v>
       </x:c>
-      <x:c r="J25"/>
+      <x:c r="J25" t="str"/>
       <x:c r="K25" t="str">
         <x:v>Internship / Placement</x:v>
       </x:c>
@@ -1460,8 +1442,8 @@
       <x:c r="O25" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="P25"/>
-      <x:c r="Q25"/>
+      <x:c r="P25" t="str"/>
+      <x:c r="Q25" t="str"/>
     </x:row>
     <x:row r="26">
       <x:c r="A26" t="str">
@@ -1476,7 +1458,7 @@
       <x:c r="D26" t="str">
         <x:v>17 July 2026</x:v>
       </x:c>
-      <x:c r="E26"/>
+      <x:c r="E26" t="str"/>
       <x:c r="F26" t="str">
         <x:v>Lahore Campus</x:v>
       </x:c>
@@ -1489,7 +1471,7 @@
       <x:c r="I26" t="str">
         <x:v>Foc Dot Lhr</x:v>
       </x:c>
-      <x:c r="J26"/>
+      <x:c r="J26" t="str"/>
       <x:c r="K26" t="str">
         <x:v>Internship / Placement</x:v>
       </x:c>
@@ -1505,8 +1487,8 @@
       <x:c r="O26" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="P26"/>
-      <x:c r="Q26"/>
+      <x:c r="P26" t="str"/>
+      <x:c r="Q26" t="str"/>
     </x:row>
     <x:row r="27">
       <x:c r="A27" t="str">
@@ -1521,7 +1503,7 @@
       <x:c r="D27" t="str">
         <x:v>17 July 2026</x:v>
       </x:c>
-      <x:c r="E27"/>
+      <x:c r="E27" t="str"/>
       <x:c r="F27" t="str">
         <x:v>Lahore Campus</x:v>
       </x:c>
@@ -1534,7 +1516,7 @@
       <x:c r="I27" t="str">
         <x:v>Foc Dot Lhr</x:v>
       </x:c>
-      <x:c r="J27"/>
+      <x:c r="J27" t="str"/>
       <x:c r="K27" t="str">
         <x:v>Internship / Placement</x:v>
       </x:c>
@@ -1550,8 +1532,8 @@
       <x:c r="O27" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="P27"/>
-      <x:c r="Q27"/>
+      <x:c r="P27" t="str"/>
+      <x:c r="Q27" t="str"/>
     </x:row>
     <x:row r="28">
       <x:c r="A28" t="str">
@@ -1566,7 +1548,7 @@
       <x:c r="D28" t="str">
         <x:v>17 July 2026</x:v>
       </x:c>
-      <x:c r="E28"/>
+      <x:c r="E28" t="str"/>
       <x:c r="F28" t="str">
         <x:v>Lahore Campus</x:v>
       </x:c>
@@ -1579,7 +1561,7 @@
       <x:c r="I28" t="str">
         <x:v>Foc Dot Lhr</x:v>
       </x:c>
-      <x:c r="J28"/>
+      <x:c r="J28" t="str"/>
       <x:c r="K28" t="str">
         <x:v>Internship / Placement</x:v>
       </x:c>
@@ -1595,8 +1577,8 @@
       <x:c r="O28" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="P28"/>
-      <x:c r="Q28"/>
+      <x:c r="P28" t="str"/>
+      <x:c r="Q28" t="str"/>
     </x:row>
     <x:row r="29">
       <x:c r="A29" t="str">
@@ -1611,7 +1593,7 @@
       <x:c r="D29" t="str">
         <x:v>17 July 2026</x:v>
       </x:c>
-      <x:c r="E29"/>
+      <x:c r="E29" t="str"/>
       <x:c r="F29" t="str">
         <x:v>Lahore Campus</x:v>
       </x:c>
@@ -1624,7 +1606,7 @@
       <x:c r="I29" t="str">
         <x:v>Foc Dot Lhr</x:v>
       </x:c>
-      <x:c r="J29"/>
+      <x:c r="J29" t="str"/>
       <x:c r="K29" t="str">
         <x:v>Internship / Placement</x:v>
       </x:c>
@@ -1640,8 +1622,8 @@
       <x:c r="O29" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="P29"/>
-      <x:c r="Q29"/>
+      <x:c r="P29" t="str"/>
+      <x:c r="Q29" t="str"/>
     </x:row>
     <x:row r="30">
       <x:c r="A30" t="str">
@@ -1656,7 +1638,7 @@
       <x:c r="D30" t="str">
         <x:v>17 July 2026</x:v>
       </x:c>
-      <x:c r="E30"/>
+      <x:c r="E30" t="str"/>
       <x:c r="F30" t="str">
         <x:v>Lahore Campus</x:v>
       </x:c>
@@ -1669,7 +1651,7 @@
       <x:c r="I30" t="str">
         <x:v>Foc Dot Lhr</x:v>
       </x:c>
-      <x:c r="J30"/>
+      <x:c r="J30" t="str"/>
       <x:c r="K30" t="str">
         <x:v>Internship / Placement</x:v>
       </x:c>
@@ -1685,8 +1667,8 @@
       <x:c r="O30" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="P30"/>
-      <x:c r="Q30"/>
+      <x:c r="P30" t="str"/>
+      <x:c r="Q30" t="str"/>
     </x:row>
     <x:row r="31">
       <x:c r="A31" t="str">
@@ -1701,7 +1683,7 @@
       <x:c r="D31" t="str">
         <x:v>17 July 2026</x:v>
       </x:c>
-      <x:c r="E31"/>
+      <x:c r="E31" t="str"/>
       <x:c r="F31" t="str">
         <x:v>Lahore Campus</x:v>
       </x:c>
@@ -1714,7 +1696,7 @@
       <x:c r="I31" t="str">
         <x:v>Foc Dot Lhr</x:v>
       </x:c>
-      <x:c r="J31"/>
+      <x:c r="J31" t="str"/>
       <x:c r="K31" t="str">
         <x:v>Internship / Placement</x:v>
       </x:c>
@@ -1730,8 +1712,8 @@
       <x:c r="O31" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="P31"/>
-      <x:c r="Q31"/>
+      <x:c r="P31" t="str"/>
+      <x:c r="Q31" t="str"/>
     </x:row>
     <x:row r="32">
       <x:c r="A32" t="str">
@@ -1746,7 +1728,7 @@
       <x:c r="D32" t="str">
         <x:v>17 July 2026</x:v>
       </x:c>
-      <x:c r="E32"/>
+      <x:c r="E32" t="str"/>
       <x:c r="F32" t="str">
         <x:v>Lahore Campus</x:v>
       </x:c>
@@ -1759,7 +1741,7 @@
       <x:c r="I32" t="str">
         <x:v>Foc Dot Lhr</x:v>
       </x:c>
-      <x:c r="J32"/>
+      <x:c r="J32" t="str"/>
       <x:c r="K32" t="str">
         <x:v>Internship / Placement</x:v>
       </x:c>
@@ -1775,8 +1757,8 @@
       <x:c r="O32" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="P32"/>
-      <x:c r="Q32"/>
+      <x:c r="P32" t="str"/>
+      <x:c r="Q32" t="str"/>
     </x:row>
     <x:row r="33">
       <x:c r="A33" t="str">
@@ -1791,7 +1773,7 @@
       <x:c r="D33" t="str">
         <x:v>17 July 2026</x:v>
       </x:c>
-      <x:c r="E33"/>
+      <x:c r="E33" t="str"/>
       <x:c r="F33" t="str">
         <x:v>Lahore Campus</x:v>
       </x:c>
@@ -1804,7 +1786,7 @@
       <x:c r="I33" t="str">
         <x:v>Foc Dot Lhr</x:v>
       </x:c>
-      <x:c r="J33"/>
+      <x:c r="J33" t="str"/>
       <x:c r="K33" t="str">
         <x:v>Internship / Placement</x:v>
       </x:c>
@@ -1820,8 +1802,8 @@
       <x:c r="O33" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="P33"/>
-      <x:c r="Q33"/>
+      <x:c r="P33" t="str"/>
+      <x:c r="Q33" t="str"/>
     </x:row>
     <x:row r="34">
       <x:c r="A34" t="str">
@@ -1836,7 +1818,7 @@
       <x:c r="D34" t="str">
         <x:v>17 July 2026</x:v>
       </x:c>
-      <x:c r="E34"/>
+      <x:c r="E34" t="str"/>
       <x:c r="F34" t="str">
         <x:v>Lahore Campus</x:v>
       </x:c>
@@ -1849,7 +1831,7 @@
       <x:c r="I34" t="str">
         <x:v>Foc Dot Lhr</x:v>
       </x:c>
-      <x:c r="J34"/>
+      <x:c r="J34" t="str"/>
       <x:c r="K34" t="str">
         <x:v>Internship / Placement</x:v>
       </x:c>
@@ -1865,8 +1847,8 @@
       <x:c r="O34" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="P34"/>
-      <x:c r="Q34"/>
+      <x:c r="P34" t="str"/>
+      <x:c r="Q34" t="str"/>
     </x:row>
     <x:row r="35">
       <x:c r="A35" t="str">
@@ -1881,7 +1863,7 @@
       <x:c r="D35" t="str">
         <x:v>17 July 2026</x:v>
       </x:c>
-      <x:c r="E35"/>
+      <x:c r="E35" t="str"/>
       <x:c r="F35" t="str">
         <x:v>Lahore Campus</x:v>
       </x:c>
@@ -1894,7 +1876,7 @@
       <x:c r="I35" t="str">
         <x:v>Foc Dot Lhr</x:v>
       </x:c>
-      <x:c r="J35"/>
+      <x:c r="J35" t="str"/>
       <x:c r="K35" t="str">
         <x:v>Internship / Placement</x:v>
       </x:c>
@@ -1910,8 +1892,8 @@
       <x:c r="O35" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="P35"/>
-      <x:c r="Q35"/>
+      <x:c r="P35" t="str"/>
+      <x:c r="Q35" t="str"/>
     </x:row>
     <x:row r="36">
       <x:c r="A36" t="str">
@@ -1926,7 +1908,7 @@
       <x:c r="D36" t="str">
         <x:v>17 July 2026</x:v>
       </x:c>
-      <x:c r="E36"/>
+      <x:c r="E36" t="str"/>
       <x:c r="F36" t="str">
         <x:v>Lahore Campus</x:v>
       </x:c>
@@ -1939,7 +1921,7 @@
       <x:c r="I36" t="str">
         <x:v>Foc Dot Lhr</x:v>
       </x:c>
-      <x:c r="J36"/>
+      <x:c r="J36" t="str"/>
       <x:c r="K36" t="str">
         <x:v>Internship / Placement</x:v>
       </x:c>
@@ -1955,8 +1937,8 @@
       <x:c r="O36" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="P36"/>
-      <x:c r="Q36"/>
+      <x:c r="P36" t="str"/>
+      <x:c r="Q36" t="str"/>
     </x:row>
     <x:row r="37">
       <x:c r="A37" t="str">
@@ -1971,7 +1953,7 @@
       <x:c r="D37" t="str">
         <x:v>17 July 2026</x:v>
       </x:c>
-      <x:c r="E37"/>
+      <x:c r="E37" t="str"/>
       <x:c r="F37" t="str">
         <x:v>Lahore Campus</x:v>
       </x:c>
@@ -1984,7 +1966,7 @@
       <x:c r="I37" t="str">
         <x:v>Foc Dot Lhr</x:v>
       </x:c>
-      <x:c r="J37"/>
+      <x:c r="J37" t="str"/>
       <x:c r="K37" t="str">
         <x:v>Internship / Placement</x:v>
       </x:c>
@@ -2000,8 +1982,8 @@
       <x:c r="O37" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="P37"/>
-      <x:c r="Q37"/>
+      <x:c r="P37" t="str"/>
+      <x:c r="Q37" t="str"/>
     </x:row>
     <x:row r="38">
       <x:c r="A38" t="str">
@@ -2016,7 +1998,7 @@
       <x:c r="D38" t="str">
         <x:v>17 July 2026</x:v>
       </x:c>
-      <x:c r="E38"/>
+      <x:c r="E38" t="str"/>
       <x:c r="F38" t="str">
         <x:v>Lahore Campus</x:v>
       </x:c>
@@ -2029,7 +2011,7 @@
       <x:c r="I38" t="str">
         <x:v>Foc Dot Lhr</x:v>
       </x:c>
-      <x:c r="J38"/>
+      <x:c r="J38" t="str"/>
       <x:c r="K38" t="str">
         <x:v>Internship / Placement</x:v>
       </x:c>
@@ -2045,8 +2027,8 @@
       <x:c r="O38" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="P38"/>
-      <x:c r="Q38"/>
+      <x:c r="P38" t="str"/>
+      <x:c r="Q38" t="str"/>
     </x:row>
     <x:row r="39">
       <x:c r="A39" t="str">
@@ -2061,7 +2043,7 @@
       <x:c r="D39" t="str">
         <x:v>17 July 2026</x:v>
       </x:c>
-      <x:c r="E39"/>
+      <x:c r="E39" t="str"/>
       <x:c r="F39" t="str">
         <x:v>Lahore Campus</x:v>
       </x:c>
@@ -2074,7 +2056,7 @@
       <x:c r="I39" t="str">
         <x:v>Foc Dot Lhr</x:v>
       </x:c>
-      <x:c r="J39"/>
+      <x:c r="J39" t="str"/>
       <x:c r="K39" t="str">
         <x:v>Internship / Placement</x:v>
       </x:c>
@@ -2090,8 +2072,8 @@
       <x:c r="O39" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="P39"/>
-      <x:c r="Q39"/>
+      <x:c r="P39" t="str"/>
+      <x:c r="Q39" t="str"/>
     </x:row>
     <x:row r="40">
       <x:c r="A40" t="str">
@@ -2106,7 +2088,7 @@
       <x:c r="D40" t="str">
         <x:v>17 July 2026</x:v>
       </x:c>
-      <x:c r="E40"/>
+      <x:c r="E40" t="str"/>
       <x:c r="F40" t="str">
         <x:v>Lahore Campus</x:v>
       </x:c>
@@ -2119,7 +2101,7 @@
       <x:c r="I40" t="str">
         <x:v>Foc Dot Lhr</x:v>
       </x:c>
-      <x:c r="J40"/>
+      <x:c r="J40" t="str"/>
       <x:c r="K40" t="str">
         <x:v>Internship / Placement</x:v>
       </x:c>
@@ -2135,8 +2117,8 @@
       <x:c r="O40" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="P40"/>
-      <x:c r="Q40"/>
+      <x:c r="P40" t="str"/>
+      <x:c r="Q40" t="str"/>
     </x:row>
     <x:row r="41">
       <x:c r="A41" t="str">
@@ -2151,7 +2133,7 @@
       <x:c r="D41" t="str">
         <x:v>17 July 2026</x:v>
       </x:c>
-      <x:c r="E41"/>
+      <x:c r="E41" t="str"/>
       <x:c r="F41" t="str">
         <x:v>Lahore Campus</x:v>
       </x:c>
@@ -2164,7 +2146,7 @@
       <x:c r="I41" t="str">
         <x:v>Foc Dot Lhr</x:v>
       </x:c>
-      <x:c r="J41"/>
+      <x:c r="J41" t="str"/>
       <x:c r="K41" t="str">
         <x:v>Internship / Placement</x:v>
       </x:c>
@@ -2180,8 +2162,8 @@
       <x:c r="O41" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="P41"/>
-      <x:c r="Q41"/>
+      <x:c r="P41" t="str"/>
+      <x:c r="Q41" t="str"/>
     </x:row>
     <x:row r="42">
       <x:c r="A42" t="str">
@@ -2196,7 +2178,7 @@
       <x:c r="D42" t="str">
         <x:v>17 July 2026</x:v>
       </x:c>
-      <x:c r="E42"/>
+      <x:c r="E42" t="str"/>
       <x:c r="F42" t="str">
         <x:v>Lahore Campus</x:v>
       </x:c>
@@ -2209,7 +2191,7 @@
       <x:c r="I42" t="str">
         <x:v>Foc Dot Lhr</x:v>
       </x:c>
-      <x:c r="J42"/>
+      <x:c r="J42" t="str"/>
       <x:c r="K42" t="str">
         <x:v>Internship / Placement</x:v>
       </x:c>
@@ -2225,8 +2207,8 @@
       <x:c r="O42" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="P42"/>
-      <x:c r="Q42"/>
+      <x:c r="P42" t="str"/>
+      <x:c r="Q42" t="str"/>
     </x:row>
     <x:row r="43">
       <x:c r="A43" t="str">
@@ -2241,7 +2223,7 @@
       <x:c r="D43" t="str">
         <x:v>17 July 2026</x:v>
       </x:c>
-      <x:c r="E43"/>
+      <x:c r="E43" t="str"/>
       <x:c r="F43" t="str">
         <x:v>Lahore Campus</x:v>
       </x:c>
@@ -2254,7 +2236,7 @@
       <x:c r="I43" t="str">
         <x:v>Foc Dot Lhr</x:v>
       </x:c>
-      <x:c r="J43"/>
+      <x:c r="J43" t="str"/>
       <x:c r="K43" t="str">
         <x:v>Internship / Placement</x:v>
       </x:c>
@@ -2270,8 +2252,8 @@
       <x:c r="O43" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="P43"/>
-      <x:c r="Q43"/>
+      <x:c r="P43" t="str"/>
+      <x:c r="Q43" t="str"/>
     </x:row>
     <x:row r="44">
       <x:c r="A44" t="str">
@@ -2286,7 +2268,7 @@
       <x:c r="D44" t="str">
         <x:v>17 July 2026</x:v>
       </x:c>
-      <x:c r="E44"/>
+      <x:c r="E44" t="str"/>
       <x:c r="F44" t="str">
         <x:v>Lahore Campus</x:v>
       </x:c>
@@ -2299,7 +2281,7 @@
       <x:c r="I44" t="str">
         <x:v>Foc Dot Lhr</x:v>
       </x:c>
-      <x:c r="J44"/>
+      <x:c r="J44" t="str"/>
       <x:c r="K44" t="str">
         <x:v>Internship / Placement</x:v>
       </x:c>
@@ -2315,8 +2297,8 @@
       <x:c r="O44" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="P44"/>
-      <x:c r="Q44"/>
+      <x:c r="P44" t="str"/>
+      <x:c r="Q44" t="str"/>
     </x:row>
     <x:row r="45">
       <x:c r="A45" t="str">
@@ -2331,7 +2313,7 @@
       <x:c r="D45" t="str">
         <x:v>17 July 2026</x:v>
       </x:c>
-      <x:c r="E45"/>
+      <x:c r="E45" t="str"/>
       <x:c r="F45" t="str">
         <x:v>Lahore Campus</x:v>
       </x:c>
@@ -2344,7 +2326,7 @@
       <x:c r="I45" t="str">
         <x:v>Foc Dot Lhr</x:v>
       </x:c>
-      <x:c r="J45"/>
+      <x:c r="J45" t="str"/>
       <x:c r="K45" t="str">
         <x:v>Internship / Placement</x:v>
       </x:c>
@@ -2360,8 +2342,8 @@
       <x:c r="O45" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="P45"/>
-      <x:c r="Q45"/>
+      <x:c r="P45" t="str"/>
+      <x:c r="Q45" t="str"/>
     </x:row>
     <x:row r="46">
       <x:c r="A46" t="str">
@@ -2376,7 +2358,7 @@
       <x:c r="D46" t="str">
         <x:v>17 July 2026</x:v>
       </x:c>
-      <x:c r="E46"/>
+      <x:c r="E46" t="str"/>
       <x:c r="F46" t="str">
         <x:v>Lahore Campus</x:v>
       </x:c>
@@ -2389,7 +2371,7 @@
       <x:c r="I46" t="str">
         <x:v>Foc Dot Lhr</x:v>
       </x:c>
-      <x:c r="J46"/>
+      <x:c r="J46" t="str"/>
       <x:c r="K46" t="str">
         <x:v>Internship / Placement</x:v>
       </x:c>
@@ -2405,8 +2387,8 @@
       <x:c r="O46" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="P46"/>
-      <x:c r="Q46"/>
+      <x:c r="P46" t="str"/>
+      <x:c r="Q46" t="str"/>
     </x:row>
     <x:row r="47">
       <x:c r="A47" t="str">
@@ -2421,7 +2403,7 @@
       <x:c r="D47" t="str">
         <x:v>17 July 2026</x:v>
       </x:c>
-      <x:c r="E47"/>
+      <x:c r="E47" t="str"/>
       <x:c r="F47" t="str">
         <x:v>Lahore Campus</x:v>
       </x:c>
@@ -2434,7 +2416,7 @@
       <x:c r="I47" t="str">
         <x:v>Foc Dot Lhr</x:v>
       </x:c>
-      <x:c r="J47"/>
+      <x:c r="J47" t="str"/>
       <x:c r="K47" t="str">
         <x:v>Internship / Placement</x:v>
       </x:c>
@@ -2450,8 +2432,8 @@
       <x:c r="O47" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="P47"/>
-      <x:c r="Q47"/>
+      <x:c r="P47" t="str"/>
+      <x:c r="Q47" t="str"/>
     </x:row>
     <x:row r="48">
       <x:c r="A48" t="str">
@@ -2466,7 +2448,7 @@
       <x:c r="D48" t="str">
         <x:v>17 July 2026</x:v>
       </x:c>
-      <x:c r="E48"/>
+      <x:c r="E48" t="str"/>
       <x:c r="F48" t="str">
         <x:v>Lahore Campus</x:v>
       </x:c>
@@ -2479,7 +2461,7 @@
       <x:c r="I48" t="str">
         <x:v>Foc Dot Lhr</x:v>
       </x:c>
-      <x:c r="J48"/>
+      <x:c r="J48" t="str"/>
       <x:c r="K48" t="str">
         <x:v>Internship / Placement</x:v>
       </x:c>
@@ -2495,8 +2477,8 @@
       <x:c r="O48" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="P48"/>
-      <x:c r="Q48"/>
+      <x:c r="P48" t="str"/>
+      <x:c r="Q48" t="str"/>
     </x:row>
     <x:row r="49">
       <x:c r="A49" t="str">
@@ -2511,7 +2493,7 @@
       <x:c r="D49" t="str">
         <x:v>17 July 2026</x:v>
       </x:c>
-      <x:c r="E49"/>
+      <x:c r="E49" t="str"/>
       <x:c r="F49" t="str">
         <x:v>Lahore Campus</x:v>
       </x:c>
@@ -2524,7 +2506,7 @@
       <x:c r="I49" t="str">
         <x:v>Foc Dot Lhr</x:v>
       </x:c>
-      <x:c r="J49"/>
+      <x:c r="J49" t="str"/>
       <x:c r="K49" t="str">
         <x:v>Internship / Placement</x:v>
       </x:c>
@@ -2540,8 +2522,8 @@
       <x:c r="O49" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="P49"/>
-      <x:c r="Q49"/>
+      <x:c r="P49" t="str"/>
+      <x:c r="Q49" t="str"/>
     </x:row>
     <x:row r="50">
       <x:c r="A50" t="str">
@@ -2556,7 +2538,7 @@
       <x:c r="D50" t="str">
         <x:v>17 July 2026</x:v>
       </x:c>
-      <x:c r="E50"/>
+      <x:c r="E50" t="str"/>
       <x:c r="F50" t="str">
         <x:v>Lahore Campus</x:v>
       </x:c>
@@ -2569,7 +2551,7 @@
       <x:c r="I50" t="str">
         <x:v>Foc Dot Lhr</x:v>
       </x:c>
-      <x:c r="J50"/>
+      <x:c r="J50" t="str"/>
       <x:c r="K50" t="str">
         <x:v>Internship / Placement</x:v>
       </x:c>
@@ -2585,8 +2567,8 @@
       <x:c r="O50" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="P50"/>
-      <x:c r="Q50"/>
+      <x:c r="P50" t="str"/>
+      <x:c r="Q50" t="str"/>
     </x:row>
     <x:row r="51">
       <x:c r="A51" t="str">
@@ -2601,7 +2583,7 @@
       <x:c r="D51" t="str">
         <x:v>17 July 2026</x:v>
       </x:c>
-      <x:c r="E51"/>
+      <x:c r="E51" t="str"/>
       <x:c r="F51" t="str">
         <x:v>Lahore Campus</x:v>
       </x:c>
@@ -2614,7 +2596,7 @@
       <x:c r="I51" t="str">
         <x:v>Foc Dot Lhr</x:v>
       </x:c>
-      <x:c r="J51"/>
+      <x:c r="J51" t="str"/>
       <x:c r="K51" t="str">
         <x:v>Internship / Placement</x:v>
       </x:c>
@@ -2624,12 +2606,12 @@
       <x:c r="M51" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="N51"/>
+      <x:c r="N51" t="str"/>
       <x:c r="O51" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="P51"/>
-      <x:c r="Q51"/>
+      <x:c r="P51" t="str"/>
+      <x:c r="Q51" t="str"/>
     </x:row>
     <x:row r="52">
       <x:c r="A52" t="str">
@@ -2644,7 +2626,7 @@
       <x:c r="D52" t="str">
         <x:v>17 July 2026</x:v>
       </x:c>
-      <x:c r="E52"/>
+      <x:c r="E52" t="str"/>
       <x:c r="F52" t="str">
         <x:v>Lahore Campus</x:v>
       </x:c>
@@ -2657,7 +2639,7 @@
       <x:c r="I52" t="str">
         <x:v>Foc Dot Lhr</x:v>
       </x:c>
-      <x:c r="J52"/>
+      <x:c r="J52" t="str"/>
       <x:c r="K52" t="str">
         <x:v>Internship / Placement</x:v>
       </x:c>
@@ -2673,8 +2655,8 @@
       <x:c r="O52" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="P52"/>
-      <x:c r="Q52"/>
+      <x:c r="P52" t="str"/>
+      <x:c r="Q52" t="str"/>
     </x:row>
     <x:row r="53">
       <x:c r="A53" t="str">
@@ -2689,7 +2671,7 @@
       <x:c r="D53" t="str">
         <x:v>17 July 2026</x:v>
       </x:c>
-      <x:c r="E53"/>
+      <x:c r="E53" t="str"/>
       <x:c r="F53" t="str">
         <x:v>Lahore Campus</x:v>
       </x:c>
@@ -2702,7 +2684,7 @@
       <x:c r="I53" t="str">
         <x:v>Foc Dot Lhr</x:v>
       </x:c>
-      <x:c r="J53"/>
+      <x:c r="J53" t="str"/>
       <x:c r="K53" t="str">
         <x:v>Internship / Placement</x:v>
       </x:c>
@@ -2718,8 +2700,8 @@
       <x:c r="O53" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="P53"/>
-      <x:c r="Q53"/>
+      <x:c r="P53" t="str"/>
+      <x:c r="Q53" t="str"/>
     </x:row>
     <x:row r="54">
       <x:c r="A54" t="str">
@@ -2734,7 +2716,7 @@
       <x:c r="D54" t="str">
         <x:v>17 July 2026</x:v>
       </x:c>
-      <x:c r="E54"/>
+      <x:c r="E54" t="str"/>
       <x:c r="F54" t="str">
         <x:v>Lahore Campus</x:v>
       </x:c>
@@ -2747,7 +2729,7 @@
       <x:c r="I54" t="str">
         <x:v>Foc Dot Lhr</x:v>
       </x:c>
-      <x:c r="J54"/>
+      <x:c r="J54" t="str"/>
       <x:c r="K54" t="str">
         <x:v>Internship / Placement</x:v>
       </x:c>
@@ -2763,8 +2745,8 @@
       <x:c r="O54" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="P54"/>
-      <x:c r="Q54"/>
+      <x:c r="P54" t="str"/>
+      <x:c r="Q54" t="str"/>
     </x:row>
     <x:row r="55">
       <x:c r="A55" t="str">
@@ -2779,7 +2761,7 @@
       <x:c r="D55" t="str">
         <x:v>17 July 2026</x:v>
       </x:c>
-      <x:c r="E55"/>
+      <x:c r="E55" t="str"/>
       <x:c r="F55" t="str">
         <x:v>Lahore Campus</x:v>
       </x:c>
@@ -2792,7 +2774,7 @@
       <x:c r="I55" t="str">
         <x:v>Foc Dot Lhr</x:v>
       </x:c>
-      <x:c r="J55"/>
+      <x:c r="J55" t="str"/>
       <x:c r="K55" t="str">
         <x:v>Internship / Placement</x:v>
       </x:c>
@@ -2808,8 +2790,8 @@
       <x:c r="O55" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="P55"/>
-      <x:c r="Q55"/>
+      <x:c r="P55" t="str"/>
+      <x:c r="Q55" t="str"/>
     </x:row>
     <x:row r="56">
       <x:c r="A56" t="str">
@@ -2824,7 +2806,7 @@
       <x:c r="D56" t="str">
         <x:v>17 July 2026</x:v>
       </x:c>
-      <x:c r="E56"/>
+      <x:c r="E56" t="str"/>
       <x:c r="F56" t="str">
         <x:v>Lahore Campus</x:v>
       </x:c>
@@ -2837,7 +2819,7 @@
       <x:c r="I56" t="str">
         <x:v>Foc Dot Lhr</x:v>
       </x:c>
-      <x:c r="J56"/>
+      <x:c r="J56" t="str"/>
       <x:c r="K56" t="str">
         <x:v>Internship / Placement</x:v>
       </x:c>
@@ -2853,8 +2835,8 @@
       <x:c r="O56" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="P56"/>
-      <x:c r="Q56"/>
+      <x:c r="P56" t="str"/>
+      <x:c r="Q56" t="str"/>
     </x:row>
     <x:row r="57">
       <x:c r="A57" t="str">
@@ -2869,7 +2851,7 @@
       <x:c r="D57" t="str">
         <x:v>17 July 2026</x:v>
       </x:c>
-      <x:c r="E57"/>
+      <x:c r="E57" t="str"/>
       <x:c r="F57" t="str">
         <x:v>Lahore Campus</x:v>
       </x:c>
@@ -2882,7 +2864,7 @@
       <x:c r="I57" t="str">
         <x:v>Foc Dot Lhr</x:v>
       </x:c>
-      <x:c r="J57"/>
+      <x:c r="J57" t="str"/>
       <x:c r="K57" t="str">
         <x:v>Internship / Placement</x:v>
       </x:c>
@@ -2898,8 +2880,8 @@
       <x:c r="O57" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="P57"/>
-      <x:c r="Q57"/>
+      <x:c r="P57" t="str"/>
+      <x:c r="Q57" t="str"/>
     </x:row>
     <x:row r="58">
       <x:c r="A58" t="str">
@@ -2914,7 +2896,7 @@
       <x:c r="D58" t="str">
         <x:v>17 July 2026</x:v>
       </x:c>
-      <x:c r="E58"/>
+      <x:c r="E58" t="str"/>
       <x:c r="F58" t="str">
         <x:v>Lahore Campus</x:v>
       </x:c>
@@ -2927,7 +2909,7 @@
       <x:c r="I58" t="str">
         <x:v>Foc Dot Lhr</x:v>
       </x:c>
-      <x:c r="J58"/>
+      <x:c r="J58" t="str"/>
       <x:c r="K58" t="str">
         <x:v>Internship / Placement</x:v>
       </x:c>
@@ -2943,8 +2925,8 @@
       <x:c r="O58" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="P58"/>
-      <x:c r="Q58"/>
+      <x:c r="P58" t="str"/>
+      <x:c r="Q58" t="str"/>
     </x:row>
     <x:row r="59">
       <x:c r="A59" t="str">
@@ -2959,7 +2941,7 @@
       <x:c r="D59" t="str">
         <x:v>17 July 2026</x:v>
       </x:c>
-      <x:c r="E59"/>
+      <x:c r="E59" t="str"/>
       <x:c r="F59" t="str">
         <x:v>Lahore Campus</x:v>
       </x:c>
@@ -2972,7 +2954,7 @@
       <x:c r="I59" t="str">
         <x:v>Foc Dot Lhr</x:v>
       </x:c>
-      <x:c r="J59"/>
+      <x:c r="J59" t="str"/>
       <x:c r="K59" t="str">
         <x:v>Internship / Placement</x:v>
       </x:c>
@@ -2988,8 +2970,8 @@
       <x:c r="O59" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="P59"/>
-      <x:c r="Q59"/>
+      <x:c r="P59" t="str"/>
+      <x:c r="Q59" t="str"/>
     </x:row>
     <x:row r="60">
       <x:c r="A60" t="str">
@@ -3004,7 +2986,7 @@
       <x:c r="D60" t="str">
         <x:v>17 July 2026</x:v>
       </x:c>
-      <x:c r="E60"/>
+      <x:c r="E60" t="str"/>
       <x:c r="F60" t="str">
         <x:v>Lahore Campus</x:v>
       </x:c>
@@ -3017,7 +2999,7 @@
       <x:c r="I60" t="str">
         <x:v>Foc Dot Lhr</x:v>
       </x:c>
-      <x:c r="J60"/>
+      <x:c r="J60" t="str"/>
       <x:c r="K60" t="str">
         <x:v>Internship / Placement</x:v>
       </x:c>
@@ -3033,8 +3015,8 @@
       <x:c r="O60" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="P60"/>
-      <x:c r="Q60"/>
+      <x:c r="P60" t="str"/>
+      <x:c r="Q60" t="str"/>
     </x:row>
     <x:row r="61">
       <x:c r="A61" t="str">
@@ -3049,7 +3031,7 @@
       <x:c r="D61" t="str">
         <x:v>17 July 2026</x:v>
       </x:c>
-      <x:c r="E61"/>
+      <x:c r="E61" t="str"/>
       <x:c r="F61" t="str">
         <x:v>Lahore Campus</x:v>
       </x:c>
@@ -3062,7 +3044,7 @@
       <x:c r="I61" t="str">
         <x:v>Foc Dot Lhr</x:v>
       </x:c>
-      <x:c r="J61"/>
+      <x:c r="J61" t="str"/>
       <x:c r="K61" t="str">
         <x:v>Internship / Placement</x:v>
       </x:c>
@@ -3078,8 +3060,8 @@
       <x:c r="O61" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="P61"/>
-      <x:c r="Q61"/>
+      <x:c r="P61" t="str"/>
+      <x:c r="Q61" t="str"/>
     </x:row>
     <x:row r="62">
       <x:c r="A62" t="str">
@@ -3094,7 +3076,7 @@
       <x:c r="D62" t="str">
         <x:v>17 July 2026</x:v>
       </x:c>
-      <x:c r="E62"/>
+      <x:c r="E62" t="str"/>
       <x:c r="F62" t="str">
         <x:v>Lahore Campus</x:v>
       </x:c>
@@ -3107,7 +3089,7 @@
       <x:c r="I62" t="str">
         <x:v>Foc Dot Lhr</x:v>
       </x:c>
-      <x:c r="J62"/>
+      <x:c r="J62" t="str"/>
       <x:c r="K62" t="str">
         <x:v>Internship / Placement</x:v>
       </x:c>
@@ -3123,8 +3105,8 @@
       <x:c r="O62" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="P62"/>
-      <x:c r="Q62"/>
+      <x:c r="P62" t="str"/>
+      <x:c r="Q62" t="str"/>
     </x:row>
     <x:row r="63">
       <x:c r="A63" t="str">
@@ -3139,7 +3121,7 @@
       <x:c r="D63" t="str">
         <x:v>17 July 2026</x:v>
       </x:c>
-      <x:c r="E63"/>
+      <x:c r="E63" t="str"/>
       <x:c r="F63" t="str">
         <x:v>Lahore Campus</x:v>
       </x:c>
@@ -3152,7 +3134,7 @@
       <x:c r="I63" t="str">
         <x:v>Foc Dot Lhr</x:v>
       </x:c>
-      <x:c r="J63"/>
+      <x:c r="J63" t="str"/>
       <x:c r="K63" t="str">
         <x:v>Internship / Placement</x:v>
       </x:c>
@@ -3168,8 +3150,8 @@
       <x:c r="O63" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="P63"/>
-      <x:c r="Q63"/>
+      <x:c r="P63" t="str"/>
+      <x:c r="Q63" t="str"/>
     </x:row>
     <x:row r="64">
       <x:c r="A64" t="str">
@@ -3184,7 +3166,7 @@
       <x:c r="D64" t="str">
         <x:v>17 July 2026</x:v>
       </x:c>
-      <x:c r="E64"/>
+      <x:c r="E64" t="str"/>
       <x:c r="F64" t="str">
         <x:v>Lahore Campus</x:v>
       </x:c>
@@ -3197,7 +3179,7 @@
       <x:c r="I64" t="str">
         <x:v>Foc Dot Lhr</x:v>
       </x:c>
-      <x:c r="J64"/>
+      <x:c r="J64" t="str"/>
       <x:c r="K64" t="str">
         <x:v>Internship / Placement</x:v>
       </x:c>
@@ -3213,8 +3195,8 @@
       <x:c r="O64" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="P64"/>
-      <x:c r="Q64"/>
+      <x:c r="P64" t="str"/>
+      <x:c r="Q64" t="str"/>
     </x:row>
     <x:row r="65">
       <x:c r="A65" t="str">
@@ -3229,7 +3211,7 @@
       <x:c r="D65" t="str">
         <x:v>17 July 2026</x:v>
       </x:c>
-      <x:c r="E65"/>
+      <x:c r="E65" t="str"/>
       <x:c r="F65" t="str">
         <x:v>Lahore Campus</x:v>
       </x:c>
@@ -3242,7 +3224,7 @@
       <x:c r="I65" t="str">
         <x:v>Foc Dot Lhr</x:v>
       </x:c>
-      <x:c r="J65"/>
+      <x:c r="J65" t="str"/>
       <x:c r="K65" t="str">
         <x:v>Internship / Placement</x:v>
       </x:c>
@@ -3258,8 +3240,8 @@
       <x:c r="O65" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="P65"/>
-      <x:c r="Q65"/>
+      <x:c r="P65" t="str"/>
+      <x:c r="Q65" t="str"/>
     </x:row>
     <x:row r="66">
       <x:c r="A66" t="str">
@@ -3274,7 +3256,7 @@
       <x:c r="D66" t="str">
         <x:v>17 July 2026</x:v>
       </x:c>
-      <x:c r="E66"/>
+      <x:c r="E66" t="str"/>
       <x:c r="F66" t="str">
         <x:v>Lahore Campus</x:v>
       </x:c>
@@ -3287,7 +3269,7 @@
       <x:c r="I66" t="str">
         <x:v>Foc Dot Lhr</x:v>
       </x:c>
-      <x:c r="J66"/>
+      <x:c r="J66" t="str"/>
       <x:c r="K66" t="str">
         <x:v>Internship / Placement</x:v>
       </x:c>
@@ -3303,8 +3285,8 @@
       <x:c r="O66" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="P66"/>
-      <x:c r="Q66"/>
+      <x:c r="P66" t="str"/>
+      <x:c r="Q66" t="str"/>
     </x:row>
     <x:row r="67">
       <x:c r="A67" t="str">
@@ -3319,7 +3301,7 @@
       <x:c r="D67" t="str">
         <x:v>17 July 2026</x:v>
       </x:c>
-      <x:c r="E67"/>
+      <x:c r="E67" t="str"/>
       <x:c r="F67" t="str">
         <x:v>Lahore Campus</x:v>
       </x:c>
@@ -3332,7 +3314,7 @@
       <x:c r="I67" t="str">
         <x:v>Foc Dot Lhr</x:v>
       </x:c>
-      <x:c r="J67"/>
+      <x:c r="J67" t="str"/>
       <x:c r="K67" t="str">
         <x:v>Internship / Placement</x:v>
       </x:c>
@@ -3348,8 +3330,8 @@
       <x:c r="O67" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="P67"/>
-      <x:c r="Q67"/>
+      <x:c r="P67" t="str"/>
+      <x:c r="Q67" t="str"/>
     </x:row>
     <x:row r="68">
       <x:c r="A68" t="str">
@@ -3364,7 +3346,7 @@
       <x:c r="D68" t="str">
         <x:v>17 July 2026</x:v>
       </x:c>
-      <x:c r="E68"/>
+      <x:c r="E68" t="str"/>
       <x:c r="F68" t="str">
         <x:v>Lahore Campus</x:v>
       </x:c>
@@ -3377,7 +3359,7 @@
       <x:c r="I68" t="str">
         <x:v>Foc Dot Lhr</x:v>
       </x:c>
-      <x:c r="J68"/>
+      <x:c r="J68" t="str"/>
       <x:c r="K68" t="str">
         <x:v>Internship / Placement</x:v>
       </x:c>
@@ -3393,8 +3375,8 @@
       <x:c r="O68" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="P68"/>
-      <x:c r="Q68"/>
+      <x:c r="P68" t="str"/>
+      <x:c r="Q68" t="str"/>
     </x:row>
     <x:row r="69">
       <x:c r="A69" t="str">
@@ -3409,7 +3391,7 @@
       <x:c r="D69" t="str">
         <x:v>17 July 2026</x:v>
       </x:c>
-      <x:c r="E69"/>
+      <x:c r="E69" t="str"/>
       <x:c r="F69" t="str">
         <x:v>Lahore Campus</x:v>
       </x:c>
@@ -3422,7 +3404,7 @@
       <x:c r="I69" t="str">
         <x:v>Foc Dot Lhr</x:v>
       </x:c>
-      <x:c r="J69"/>
+      <x:c r="J69" t="str"/>
       <x:c r="K69" t="str">
         <x:v>Internship / Placement</x:v>
       </x:c>
@@ -3438,8 +3420,8 @@
       <x:c r="O69" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="P69"/>
-      <x:c r="Q69"/>
+      <x:c r="P69" t="str"/>
+      <x:c r="Q69" t="str"/>
     </x:row>
     <x:row r="70">
       <x:c r="A70" t="str">
@@ -3454,7 +3436,7 @@
       <x:c r="D70" t="str">
         <x:v>17 July 2026</x:v>
       </x:c>
-      <x:c r="E70"/>
+      <x:c r="E70" t="str"/>
       <x:c r="F70" t="str">
         <x:v>Lahore Campus</x:v>
       </x:c>
@@ -3467,7 +3449,7 @@
       <x:c r="I70" t="str">
         <x:v>Foc Dot Lhr</x:v>
       </x:c>
-      <x:c r="J70"/>
+      <x:c r="J70" t="str"/>
       <x:c r="K70" t="str">
         <x:v>Internship / Placement</x:v>
       </x:c>
@@ -3483,8 +3465,8 @@
       <x:c r="O70" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="P70"/>
-      <x:c r="Q70"/>
+      <x:c r="P70" t="str"/>
+      <x:c r="Q70" t="str"/>
     </x:row>
     <x:row r="71">
       <x:c r="A71" t="str">
@@ -3499,7 +3481,7 @@
       <x:c r="D71" t="str">
         <x:v>17 July 2026</x:v>
       </x:c>
-      <x:c r="E71"/>
+      <x:c r="E71" t="str"/>
       <x:c r="F71" t="str">
         <x:v>Lahore Campus</x:v>
       </x:c>
@@ -3512,7 +3494,7 @@
       <x:c r="I71" t="str">
         <x:v>Foc Dot Lhr</x:v>
       </x:c>
-      <x:c r="J71"/>
+      <x:c r="J71" t="str"/>
       <x:c r="K71" t="str">
         <x:v>Internship / Placement</x:v>
       </x:c>
@@ -3528,8 +3510,8 @@
       <x:c r="O71" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="P71"/>
-      <x:c r="Q71"/>
+      <x:c r="P71" t="str"/>
+      <x:c r="Q71" t="str"/>
     </x:row>
     <x:row r="72">
       <x:c r="A72" t="str">
@@ -3544,7 +3526,7 @@
       <x:c r="D72" t="str">
         <x:v>17 July 2026</x:v>
       </x:c>
-      <x:c r="E72"/>
+      <x:c r="E72" t="str"/>
       <x:c r="F72" t="str">
         <x:v>Lahore Campus</x:v>
       </x:c>
@@ -3557,7 +3539,7 @@
       <x:c r="I72" t="str">
         <x:v>Foc Dot Lhr</x:v>
       </x:c>
-      <x:c r="J72"/>
+      <x:c r="J72" t="str"/>
       <x:c r="K72" t="str">
         <x:v>Internship / Placement</x:v>
       </x:c>
@@ -3573,8 +3555,8 @@
       <x:c r="O72" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="P72"/>
-      <x:c r="Q72"/>
+      <x:c r="P72" t="str"/>
+      <x:c r="Q72" t="str"/>
     </x:row>
     <x:row r="73">
       <x:c r="A73" t="str">
@@ -3589,7 +3571,7 @@
       <x:c r="D73" t="str">
         <x:v>17 July 2026</x:v>
       </x:c>
-      <x:c r="E73"/>
+      <x:c r="E73" t="str"/>
       <x:c r="F73" t="str">
         <x:v>Lahore Campus</x:v>
       </x:c>
@@ -3602,7 +3584,7 @@
       <x:c r="I73" t="str">
         <x:v>Foc Dot Lhr</x:v>
       </x:c>
-      <x:c r="J73"/>
+      <x:c r="J73" t="str"/>
       <x:c r="K73" t="str">
         <x:v>Internship / Placement</x:v>
       </x:c>
@@ -3618,8 +3600,8 @@
       <x:c r="O73" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="P73"/>
-      <x:c r="Q73"/>
+      <x:c r="P73" t="str"/>
+      <x:c r="Q73" t="str"/>
     </x:row>
     <x:row r="74">
       <x:c r="A74" t="str">
@@ -3634,7 +3616,7 @@
       <x:c r="D74" t="str">
         <x:v>17 July 2026</x:v>
       </x:c>
-      <x:c r="E74"/>
+      <x:c r="E74" t="str"/>
       <x:c r="F74" t="str">
         <x:v>Lahore Campus</x:v>
       </x:c>
@@ -3647,7 +3629,7 @@
       <x:c r="I74" t="str">
         <x:v>Foc Dot Lhr</x:v>
       </x:c>
-      <x:c r="J74"/>
+      <x:c r="J74" t="str"/>
       <x:c r="K74" t="str">
         <x:v>Internship / Placement</x:v>
       </x:c>
@@ -3663,8 +3645,8 @@
       <x:c r="O74" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="P74"/>
-      <x:c r="Q74"/>
+      <x:c r="P74" t="str"/>
+      <x:c r="Q74" t="str"/>
     </x:row>
     <x:row r="75">
       <x:c r="A75" t="str">
@@ -3679,7 +3661,7 @@
       <x:c r="D75" t="str">
         <x:v>17 July 2026</x:v>
       </x:c>
-      <x:c r="E75"/>
+      <x:c r="E75" t="str"/>
       <x:c r="F75" t="str">
         <x:v>Lahore Campus</x:v>
       </x:c>
@@ -3692,7 +3674,7 @@
       <x:c r="I75" t="str">
         <x:v>Foc Dot Lhr</x:v>
       </x:c>
-      <x:c r="J75"/>
+      <x:c r="J75" t="str"/>
       <x:c r="K75" t="str">
         <x:v>Internship / Placement</x:v>
       </x:c>
@@ -3708,8 +3690,8 @@
       <x:c r="O75" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="P75"/>
-      <x:c r="Q75"/>
+      <x:c r="P75" t="str"/>
+      <x:c r="Q75" t="str"/>
     </x:row>
     <x:row r="76">
       <x:c r="A76" t="str">
@@ -3724,7 +3706,7 @@
       <x:c r="D76" t="str">
         <x:v>17 July 2026</x:v>
       </x:c>
-      <x:c r="E76"/>
+      <x:c r="E76" t="str"/>
       <x:c r="F76" t="str">
         <x:v>Lahore Campus</x:v>
       </x:c>
@@ -3737,7 +3719,7 @@
       <x:c r="I76" t="str">
         <x:v>Foc Dot Lhr</x:v>
       </x:c>
-      <x:c r="J76"/>
+      <x:c r="J76" t="str"/>
       <x:c r="K76" t="str">
         <x:v>Internship / Placement</x:v>
       </x:c>
@@ -3753,8 +3735,8 @@
       <x:c r="O76" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="P76"/>
-      <x:c r="Q76"/>
+      <x:c r="P76" t="str"/>
+      <x:c r="Q76" t="str"/>
     </x:row>
     <x:row r="77">
       <x:c r="A77" t="str">
@@ -3769,7 +3751,7 @@
       <x:c r="D77" t="str">
         <x:v>17 July 2026</x:v>
       </x:c>
-      <x:c r="E77"/>
+      <x:c r="E77" t="str"/>
       <x:c r="F77" t="str">
         <x:v>Lahore Campus</x:v>
       </x:c>
@@ -3782,7 +3764,7 @@
       <x:c r="I77" t="str">
         <x:v>Foc Dot Lhr</x:v>
       </x:c>
-      <x:c r="J77"/>
+      <x:c r="J77" t="str"/>
       <x:c r="K77" t="str">
         <x:v>Internship / Placement</x:v>
       </x:c>
@@ -3798,8 +3780,8 @@
       <x:c r="O77" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="P77"/>
-      <x:c r="Q77"/>
+      <x:c r="P77" t="str"/>
+      <x:c r="Q77" t="str"/>
     </x:row>
     <x:row r="78">
       <x:c r="A78" t="str">
@@ -3814,7 +3796,7 @@
       <x:c r="D78" t="str">
         <x:v>17 July 2026</x:v>
       </x:c>
-      <x:c r="E78"/>
+      <x:c r="E78" t="str"/>
       <x:c r="F78" t="str">
         <x:v>Lahore Campus</x:v>
       </x:c>
@@ -3827,7 +3809,7 @@
       <x:c r="I78" t="str">
         <x:v>Foc Dot Lhr</x:v>
       </x:c>
-      <x:c r="J78"/>
+      <x:c r="J78" t="str"/>
       <x:c r="K78" t="str">
         <x:v>Internship / Placement</x:v>
       </x:c>
@@ -3843,8 +3825,8 @@
       <x:c r="O78" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="P78"/>
-      <x:c r="Q78"/>
+      <x:c r="P78" t="str"/>
+      <x:c r="Q78" t="str"/>
     </x:row>
     <x:row r="79">
       <x:c r="A79" t="str">
@@ -3859,7 +3841,7 @@
       <x:c r="D79" t="str">
         <x:v>17 July 2026</x:v>
       </x:c>
-      <x:c r="E79"/>
+      <x:c r="E79" t="str"/>
       <x:c r="F79" t="str">
         <x:v>Lahore Campus</x:v>
       </x:c>
@@ -3872,7 +3854,7 @@
       <x:c r="I79" t="str">
         <x:v>Foc Dot Lhr</x:v>
       </x:c>
-      <x:c r="J79"/>
+      <x:c r="J79" t="str"/>
       <x:c r="K79" t="str">
         <x:v>Internship / Placement</x:v>
       </x:c>
@@ -3888,8 +3870,8 @@
       <x:c r="O79" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="P79"/>
-      <x:c r="Q79"/>
+      <x:c r="P79" t="str"/>
+      <x:c r="Q79" t="str"/>
     </x:row>
     <x:row r="80">
       <x:c r="A80" t="str">
@@ -3904,7 +3886,7 @@
       <x:c r="D80" t="str">
         <x:v>17 July 2026</x:v>
       </x:c>
-      <x:c r="E80"/>
+      <x:c r="E80" t="str"/>
       <x:c r="F80" t="str">
         <x:v>Lahore Campus</x:v>
       </x:c>
@@ -3917,7 +3899,7 @@
       <x:c r="I80" t="str">
         <x:v>Foc Dot Lhr</x:v>
       </x:c>
-      <x:c r="J80"/>
+      <x:c r="J80" t="str"/>
       <x:c r="K80" t="str">
         <x:v>Internship / Placement</x:v>
       </x:c>
@@ -3933,8 +3915,8 @@
       <x:c r="O80" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="P80"/>
-      <x:c r="Q80"/>
+      <x:c r="P80" t="str"/>
+      <x:c r="Q80" t="str"/>
     </x:row>
     <x:row r="81">
       <x:c r="A81" t="str">
@@ -3949,7 +3931,7 @@
       <x:c r="D81" t="str">
         <x:v>17 July 2026</x:v>
       </x:c>
-      <x:c r="E81"/>
+      <x:c r="E81" t="str"/>
       <x:c r="F81" t="str">
         <x:v>Lahore Campus</x:v>
       </x:c>
@@ -3962,7 +3944,7 @@
       <x:c r="I81" t="str">
         <x:v>Foc Dot Lhr</x:v>
       </x:c>
-      <x:c r="J81"/>
+      <x:c r="J81" t="str"/>
       <x:c r="K81" t="str">
         <x:v>Internship / Placement</x:v>
       </x:c>
@@ -3978,8 +3960,8 @@
       <x:c r="O81" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="P81"/>
-      <x:c r="Q81"/>
+      <x:c r="P81" t="str"/>
+      <x:c r="Q81" t="str"/>
     </x:row>
     <x:row r="82">
       <x:c r="A82" t="str">
@@ -3994,7 +3976,7 @@
       <x:c r="D82" t="str">
         <x:v>17 July 2026</x:v>
       </x:c>
-      <x:c r="E82"/>
+      <x:c r="E82" t="str"/>
       <x:c r="F82" t="str">
         <x:v>Lahore Campus</x:v>
       </x:c>
@@ -4007,7 +3989,7 @@
       <x:c r="I82" t="str">
         <x:v>Foc Dot Lhr</x:v>
       </x:c>
-      <x:c r="J82"/>
+      <x:c r="J82" t="str"/>
       <x:c r="K82" t="str">
         <x:v>Internship / Placement</x:v>
       </x:c>
@@ -4023,8 +4005,8 @@
       <x:c r="O82" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="P82"/>
-      <x:c r="Q82"/>
+      <x:c r="P82" t="str"/>
+      <x:c r="Q82" t="str"/>
     </x:row>
     <x:row r="83">
       <x:c r="A83" t="str">
@@ -4039,7 +4021,7 @@
       <x:c r="D83" t="str">
         <x:v>17 July 2026</x:v>
       </x:c>
-      <x:c r="E83"/>
+      <x:c r="E83" t="str"/>
       <x:c r="F83" t="str">
         <x:v>Lahore Campus</x:v>
       </x:c>
@@ -4052,7 +4034,7 @@
       <x:c r="I83" t="str">
         <x:v>Foc Dot Lhr</x:v>
       </x:c>
-      <x:c r="J83"/>
+      <x:c r="J83" t="str"/>
       <x:c r="K83" t="str">
         <x:v>Internship / Placement</x:v>
       </x:c>
@@ -4068,8 +4050,8 @@
       <x:c r="O83" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="P83"/>
-      <x:c r="Q83"/>
+      <x:c r="P83" t="str"/>
+      <x:c r="Q83" t="str"/>
     </x:row>
     <x:row r="84">
       <x:c r="A84" t="str">
@@ -4084,7 +4066,7 @@
       <x:c r="D84" t="str">
         <x:v>17 July 2026</x:v>
       </x:c>
-      <x:c r="E84"/>
+      <x:c r="E84" t="str"/>
       <x:c r="F84" t="str">
         <x:v>Lahore Campus</x:v>
       </x:c>
@@ -4097,7 +4079,7 @@
       <x:c r="I84" t="str">
         <x:v>Foc Dot Lhr</x:v>
       </x:c>
-      <x:c r="J84"/>
+      <x:c r="J84" t="str"/>
       <x:c r="K84" t="str">
         <x:v>Internship / Placement</x:v>
       </x:c>
@@ -4113,8 +4095,8 @@
       <x:c r="O84" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="P84"/>
-      <x:c r="Q84"/>
+      <x:c r="P84" t="str"/>
+      <x:c r="Q84" t="str"/>
     </x:row>
     <x:row r="85">
       <x:c r="A85" t="str">
@@ -4129,7 +4111,7 @@
       <x:c r="D85" t="str">
         <x:v>17 July 2026</x:v>
       </x:c>
-      <x:c r="E85"/>
+      <x:c r="E85" t="str"/>
       <x:c r="F85" t="str">
         <x:v>Lahore Campus</x:v>
       </x:c>
@@ -4142,7 +4124,7 @@
       <x:c r="I85" t="str">
         <x:v>Foc Dot Lhr</x:v>
       </x:c>
-      <x:c r="J85"/>
+      <x:c r="J85" t="str"/>
       <x:c r="K85" t="str">
         <x:v>Internship / Placement</x:v>
       </x:c>
@@ -4158,8 +4140,8 @@
       <x:c r="O85" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="P85"/>
-      <x:c r="Q85"/>
+      <x:c r="P85" t="str"/>
+      <x:c r="Q85" t="str"/>
     </x:row>
     <x:row r="86">
       <x:c r="A86" t="str">
@@ -4174,7 +4156,7 @@
       <x:c r="D86" t="str">
         <x:v>17 July 2026</x:v>
       </x:c>
-      <x:c r="E86"/>
+      <x:c r="E86" t="str"/>
       <x:c r="F86" t="str">
         <x:v>Lahore Campus</x:v>
       </x:c>
@@ -4187,7 +4169,7 @@
       <x:c r="I86" t="str">
         <x:v>Foc Dot Lhr</x:v>
       </x:c>
-      <x:c r="J86"/>
+      <x:c r="J86" t="str"/>
       <x:c r="K86" t="str">
         <x:v>Internship / Placement</x:v>
       </x:c>
@@ -4203,8 +4185,8 @@
       <x:c r="O86" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="P86"/>
-      <x:c r="Q86"/>
+      <x:c r="P86" t="str"/>
+      <x:c r="Q86" t="str"/>
     </x:row>
     <x:row r="87">
       <x:c r="A87" t="str">
@@ -4219,7 +4201,7 @@
       <x:c r="D87" t="str">
         <x:v>17 July 2026</x:v>
       </x:c>
-      <x:c r="E87"/>
+      <x:c r="E87" t="str"/>
       <x:c r="F87" t="str">
         <x:v>Lahore Campus</x:v>
       </x:c>
@@ -4232,7 +4214,7 @@
       <x:c r="I87" t="str">
         <x:v>Foc Dot Lhr</x:v>
       </x:c>
-      <x:c r="J87"/>
+      <x:c r="J87" t="str"/>
       <x:c r="K87" t="str">
         <x:v>Internship / Placement</x:v>
       </x:c>
@@ -4248,8 +4230,8 @@
       <x:c r="O87" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="P87"/>
-      <x:c r="Q87"/>
+      <x:c r="P87" t="str"/>
+      <x:c r="Q87" t="str"/>
     </x:row>
     <x:row r="88">
       <x:c r="A88" t="str">
@@ -4353,7 +4335,7 @@
       <x:c r="P89" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="Q89"/>
+      <x:c r="Q89" t="str"/>
     </x:row>
     <x:row r="90">
       <x:c r="A90" t="str">
@@ -4404,7 +4386,7 @@
       <x:c r="P90" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="Q90"/>
+      <x:c r="Q90" t="str"/>
     </x:row>
     <x:row r="91">
       <x:c r="A91" t="str">
@@ -4455,7 +4437,7 @@
       <x:c r="P91" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="Q91"/>
+      <x:c r="Q91" t="str"/>
     </x:row>
     <x:row r="92">
       <x:c r="A92" t="str">
@@ -4506,7 +4488,7 @@
       <x:c r="P92" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="Q92"/>
+      <x:c r="Q92" t="str"/>
     </x:row>
     <x:row r="93">
       <x:c r="A93" t="str">
@@ -4557,7 +4539,1255 @@
       <x:c r="P93" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="Q93"/>
+      <x:c r="Q93" t="str"/>
+    </x:row>
+    <x:row r="94">
+      <x:c r="A94" t="str">
+        <x:v>PRPSTFPT101</x:v>
+      </x:c>
+      <x:c r="B94" t="str">
+        <x:v>Foc Uimlt Lhr</x:v>
+      </x:c>
+      <x:c r="C94" t="str">
+        <x:v>Approved</x:v>
+      </x:c>
+      <x:c r="D94" t="str">
+        <x:v>5 October 2026</x:v>
+      </x:c>
+      <x:c r="E94" t="str">
+        <x:v>2026-09-21</x:v>
+      </x:c>
+      <x:c r="F94" t="str">
+        <x:v>Lahore Campus</x:v>
+      </x:c>
+      <x:c r="G94" t="str">
+        <x:v>Faculty of Allied Health Sciences</x:v>
+      </x:c>
+      <x:c r="H94" t="str">
+        <x:v>University Institute of Medical Lab Technology</x:v>
+      </x:c>
+      <x:c r="I94" t="str">
+        <x:v>Foc Uimlt Lhr</x:v>
+      </x:c>
+      <x:c r="J94" t="str">
+        <x:v>Lecturer</x:v>
+      </x:c>
+      <x:c r="K94" t="str">
+        <x:v>Internship / Placement</x:v>
+      </x:c>
+      <x:c r="L94" t="str">
+        <x:v>Internship</x:v>
+      </x:c>
+      <x:c r="M94" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N94" t="str"/>
+      <x:c r="O94" t="str"/>
+      <x:c r="P94" t="str"/>
+      <x:c r="Q94" t="str"/>
+    </x:row>
+    <x:row r="95">
+      <x:c r="A95" t="str">
+        <x:v>PRPSTFPT95</x:v>
+      </x:c>
+      <x:c r="B95" t="str">
+        <x:v>Foc Dois Lhr</x:v>
+      </x:c>
+      <x:c r="C95" t="str">
+        <x:v>Pending From Linkage Officer</x:v>
+      </x:c>
+      <x:c r="D95" t="str">
+        <x:v>30 September 2026</x:v>
+      </x:c>
+      <x:c r="E95" t="str">
+        <x:v>2026-09-30</x:v>
+      </x:c>
+      <x:c r="F95" t="str">
+        <x:v>Lahore Campus</x:v>
+      </x:c>
+      <x:c r="G95" t="str">
+        <x:v>Faculty of Social Sciences</x:v>
+      </x:c>
+      <x:c r="H95" t="str">
+        <x:v>Department of Islamic Studies</x:v>
+      </x:c>
+      <x:c r="I95" t="str">
+        <x:v>Fartashia Dastagir</x:v>
+      </x:c>
+      <x:c r="J95" t="str">
+        <x:v>Research Associate</x:v>
+      </x:c>
+      <x:c r="K95" t="str">
+        <x:v>Internship / Placement</x:v>
+      </x:c>
+      <x:c r="L95" t="str">
+        <x:v>Internship</x:v>
+      </x:c>
+      <x:c r="M95" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N95" t="str"/>
+      <x:c r="O95" t="str"/>
+      <x:c r="P95" t="str"/>
+      <x:c r="Q95" t="str"/>
+    </x:row>
+    <x:row r="96">
+      <x:c r="A96" t="str">
+        <x:v>PRPSTFPT95</x:v>
+      </x:c>
+      <x:c r="B96" t="str">
+        <x:v>Foc Dois Lhr</x:v>
+      </x:c>
+      <x:c r="C96" t="str">
+        <x:v>Pending From Linkage Officer</x:v>
+      </x:c>
+      <x:c r="D96" t="str">
+        <x:v>30 September 2026</x:v>
+      </x:c>
+      <x:c r="E96" t="str">
+        <x:v>2026-09-30</x:v>
+      </x:c>
+      <x:c r="F96" t="str">
+        <x:v>Lahore Campus</x:v>
+      </x:c>
+      <x:c r="G96" t="str">
+        <x:v>Faculty of Social Sciences</x:v>
+      </x:c>
+      <x:c r="H96" t="str">
+        <x:v>Department of Islamic Studies</x:v>
+      </x:c>
+      <x:c r="I96" t="str">
+        <x:v>Fartashia Dastagir</x:v>
+      </x:c>
+      <x:c r="J96" t="str">
+        <x:v>Research Associate</x:v>
+      </x:c>
+      <x:c r="K96" t="str">
+        <x:v>Internship / Placement</x:v>
+      </x:c>
+      <x:c r="L96" t="str">
+        <x:v>Placement</x:v>
+      </x:c>
+      <x:c r="M96" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N96" t="str"/>
+      <x:c r="O96" t="str"/>
+      <x:c r="P96" t="str"/>
+      <x:c r="Q96" t="str"/>
+    </x:row>
+    <x:row r="97">
+      <x:c r="A97" t="str">
+        <x:v>PRPSTFPT84</x:v>
+      </x:c>
+      <x:c r="B97" t="str">
+        <x:v>Foc Lsn Lhr</x:v>
+      </x:c>
+      <x:c r="C97" t="str">
+        <x:v>Pending From Linkage Officer</x:v>
+      </x:c>
+      <x:c r="D97" t="str">
+        <x:v>15 September 2026</x:v>
+      </x:c>
+      <x:c r="E97" t="str">
+        <x:v>2026-02-02</x:v>
+      </x:c>
+      <x:c r="F97" t="str">
+        <x:v>Lahore Campus</x:v>
+      </x:c>
+      <x:c r="G97" t="str">
+        <x:v>Faculty of Allied Health Sciences</x:v>
+      </x:c>
+      <x:c r="H97" t="str">
+        <x:v>Lahore School of Nursing</x:v>
+      </x:c>
+      <x:c r="I97" t="str">
+        <x:v>Foc Lsn Lhr</x:v>
+      </x:c>
+      <x:c r="J97" t="str">
+        <x:v>Assistant professor</x:v>
+      </x:c>
+      <x:c r="K97" t="str">
+        <x:v>Internship / Placement</x:v>
+      </x:c>
+      <x:c r="L97" t="str">
+        <x:v>Placement</x:v>
+      </x:c>
+      <x:c r="M97" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N97" t="str"/>
+      <x:c r="O97" t="str"/>
+      <x:c r="P97" t="str"/>
+      <x:c r="Q97" t="str"/>
+    </x:row>
+    <x:row r="98">
+      <x:c r="A98" t="str">
+        <x:v>PRPSTFPT79</x:v>
+      </x:c>
+      <x:c r="B98" t="str">
+        <x:v>Foc Soca Lhr</x:v>
+      </x:c>
+      <x:c r="C98" t="str">
+        <x:v>Pending From Linkage Officer</x:v>
+      </x:c>
+      <x:c r="D98" t="str">
+        <x:v>10 September 2026</x:v>
+      </x:c>
+      <x:c r="E98" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+      <x:c r="F98" t="str">
+        <x:v>Lahore Campus</x:v>
+      </x:c>
+      <x:c r="G98" t="str">
+        <x:v>Faculty of Arts and Architecture</x:v>
+      </x:c>
+      <x:c r="H98" t="str">
+        <x:v>School of Creative Arts</x:v>
+      </x:c>
+      <x:c r="I98" t="str">
+        <x:v>Foc Sociology Lhr</x:v>
+      </x:c>
+      <x:c r="J98" t="str">
+        <x:v>Lecturer</x:v>
+      </x:c>
+      <x:c r="K98" t="str">
+        <x:v>Internship / Placement</x:v>
+      </x:c>
+      <x:c r="L98" t="str">
+        <x:v>Internship</x:v>
+      </x:c>
+      <x:c r="M98" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N98" t="str"/>
+      <x:c r="O98" t="str"/>
+      <x:c r="P98" t="str"/>
+      <x:c r="Q98" t="str"/>
+    </x:row>
+    <x:row r="99">
+      <x:c r="A99" t="str">
+        <x:v>PRPSTFPT76</x:v>
+      </x:c>
+      <x:c r="B99" t="str">
+        <x:v>Foc Soca Lhr</x:v>
+      </x:c>
+      <x:c r="C99" t="str">
+        <x:v>Pending From Linkage Officer</x:v>
+      </x:c>
+      <x:c r="D99" t="str">
+        <x:v>17 August 2026</x:v>
+      </x:c>
+      <x:c r="E99" t="str">
+        <x:v>2026-05-21</x:v>
+      </x:c>
+      <x:c r="F99" t="str">
+        <x:v>Lahore Campus</x:v>
+      </x:c>
+      <x:c r="G99" t="str">
+        <x:v>Faculty of Arts and Architecture</x:v>
+      </x:c>
+      <x:c r="H99" t="str">
+        <x:v>School of Creative Arts</x:v>
+      </x:c>
+      <x:c r="I99" t="str">
+        <x:v>Foc Soca Lhr</x:v>
+      </x:c>
+      <x:c r="J99" t="str">
+        <x:v>Assistant Professor</x:v>
+      </x:c>
+      <x:c r="K99" t="str">
+        <x:v>Internship / Placement</x:v>
+      </x:c>
+      <x:c r="L99" t="str">
+        <x:v>Internship</x:v>
+      </x:c>
+      <x:c r="M99" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N99" t="str"/>
+      <x:c r="O99" t="str"/>
+      <x:c r="P99" t="str"/>
+      <x:c r="Q99" t="str"/>
+    </x:row>
+    <x:row r="100">
+      <x:c r="A100" t="str">
+        <x:v>PRPSTFPT59</x:v>
+      </x:c>
+      <x:c r="B100" t="str">
+        <x:v>Foc Lsa Lhr</x:v>
+      </x:c>
+      <x:c r="C100" t="str">
+        <x:v>Pending From Linkage Officer</x:v>
+      </x:c>
+      <x:c r="D100" t="str">
+        <x:v>25 July 2026</x:v>
+      </x:c>
+      <x:c r="E100" t="str"/>
+      <x:c r="F100" t="str">
+        <x:v>Lahore Campus</x:v>
+      </x:c>
+      <x:c r="G100" t="str">
+        <x:v>Faculty of Management Sciences</x:v>
+      </x:c>
+      <x:c r="H100" t="str">
+        <x:v>Lahore School of Aviation</x:v>
+      </x:c>
+      <x:c r="I100" t="str">
+        <x:v>Foc Lsa Lhr</x:v>
+      </x:c>
+      <x:c r="J100" t="str">
+        <x:v>Assistant Professor</x:v>
+      </x:c>
+      <x:c r="K100" t="str">
+        <x:v>Internship / Placement</x:v>
+      </x:c>
+      <x:c r="L100" t="str">
+        <x:v>Internship</x:v>
+      </x:c>
+      <x:c r="M100" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N100" t="str"/>
+      <x:c r="O100" t="str"/>
+      <x:c r="P100" t="str"/>
+      <x:c r="Q100" t="str"/>
+    </x:row>
+    <x:row r="101">
+      <x:c r="A101" t="str">
+        <x:v>PRPSTFPT59</x:v>
+      </x:c>
+      <x:c r="B101" t="str">
+        <x:v>Foc Lsa Lhr</x:v>
+      </x:c>
+      <x:c r="C101" t="str">
+        <x:v>Pending From Linkage Officer</x:v>
+      </x:c>
+      <x:c r="D101" t="str">
+        <x:v>25 July 2026</x:v>
+      </x:c>
+      <x:c r="E101" t="str"/>
+      <x:c r="F101" t="str">
+        <x:v>Lahore Campus</x:v>
+      </x:c>
+      <x:c r="G101" t="str">
+        <x:v>Faculty of Management Sciences</x:v>
+      </x:c>
+      <x:c r="H101" t="str">
+        <x:v>Lahore School of Aviation</x:v>
+      </x:c>
+      <x:c r="I101" t="str">
+        <x:v>Foc Lsa Lhr</x:v>
+      </x:c>
+      <x:c r="J101" t="str">
+        <x:v>Assistant Professor</x:v>
+      </x:c>
+      <x:c r="K101" t="str">
+        <x:v>Internship / Placement</x:v>
+      </x:c>
+      <x:c r="L101" t="str">
+        <x:v>Placement</x:v>
+      </x:c>
+      <x:c r="M101" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N101" t="str"/>
+      <x:c r="O101" t="str"/>
+      <x:c r="P101" t="str"/>
+      <x:c r="Q101" t="str"/>
+    </x:row>
+    <x:row r="102">
+      <x:c r="A102" t="str">
+        <x:v>PRPSTFPT59</x:v>
+      </x:c>
+      <x:c r="B102" t="str">
+        <x:v>Foc Lsa Lhr</x:v>
+      </x:c>
+      <x:c r="C102" t="str">
+        <x:v>Pending From Linkage Officer</x:v>
+      </x:c>
+      <x:c r="D102" t="str">
+        <x:v>25 July 2026</x:v>
+      </x:c>
+      <x:c r="E102" t="str"/>
+      <x:c r="F102" t="str">
+        <x:v>Lahore Campus</x:v>
+      </x:c>
+      <x:c r="G102" t="str">
+        <x:v>Faculty of Management Sciences</x:v>
+      </x:c>
+      <x:c r="H102" t="str">
+        <x:v>Lahore School of Aviation</x:v>
+      </x:c>
+      <x:c r="I102" t="str">
+        <x:v>Foc Lsa Lhr</x:v>
+      </x:c>
+      <x:c r="J102" t="str">
+        <x:v>Assistant Professor</x:v>
+      </x:c>
+      <x:c r="K102" t="str">
+        <x:v>Internship / Placement</x:v>
+      </x:c>
+      <x:c r="L102" t="str">
+        <x:v>Placement</x:v>
+      </x:c>
+      <x:c r="M102" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N102" t="str"/>
+      <x:c r="O102" t="str"/>
+      <x:c r="P102" t="str"/>
+      <x:c r="Q102" t="str"/>
+    </x:row>
+    <x:row r="103">
+      <x:c r="A103" t="str">
+        <x:v>PRPSTFPT56</x:v>
+      </x:c>
+      <x:c r="B103" t="str">
+        <x:v>Foc Dhpt Lhr</x:v>
+      </x:c>
+      <x:c r="C103" t="str">
+        <x:v>Pending From Linkage Officer</x:v>
+      </x:c>
+      <x:c r="D103" t="str">
+        <x:v>23 July 2026</x:v>
+      </x:c>
+      <x:c r="E103" t="str">
+        <x:v>2026-07-23</x:v>
+      </x:c>
+      <x:c r="F103" t="str">
+        <x:v>Lahore Campus</x:v>
+      </x:c>
+      <x:c r="G103" t="str">
+        <x:v>Faculty of Allied Health Sciences</x:v>
+      </x:c>
+      <x:c r="H103" t="str">
+        <x:v>Department of Health Professional Technologies</x:v>
+      </x:c>
+      <x:c r="I103" t="str">
+        <x:v>Foc Dhpt Lhr</x:v>
+      </x:c>
+      <x:c r="J103" t="str">
+        <x:v>Senior Lecturer</x:v>
+      </x:c>
+      <x:c r="K103" t="str">
+        <x:v>Internship / Placement</x:v>
+      </x:c>
+      <x:c r="L103" t="str">
+        <x:v>Internship</x:v>
+      </x:c>
+      <x:c r="M103" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N103" t="str"/>
+      <x:c r="O103" t="str"/>
+      <x:c r="P103" t="str"/>
+      <x:c r="Q103" t="str"/>
+    </x:row>
+    <x:row r="104">
+      <x:c r="A104" t="str">
+        <x:v>PRPSTFPT55</x:v>
+      </x:c>
+      <x:c r="B104" t="str">
+        <x:v>Foc Dovs Lhr</x:v>
+      </x:c>
+      <x:c r="C104" t="str">
+        <x:v>Pending From Linkage Officer</x:v>
+      </x:c>
+      <x:c r="D104" t="str">
+        <x:v>23 July 2026</x:v>
+      </x:c>
+      <x:c r="E104" t="str">
+        <x:v>2026-07-23</x:v>
+      </x:c>
+      <x:c r="F104" t="str">
+        <x:v>Lahore Campus</x:v>
+      </x:c>
+      <x:c r="G104" t="str">
+        <x:v>Faculty of Allied Health Sciences</x:v>
+      </x:c>
+      <x:c r="H104" t="str">
+        <x:v>Department of Optometry &amp; Vision Science</x:v>
+      </x:c>
+      <x:c r="I104" t="str">
+        <x:v>Foc Dovs Lhr</x:v>
+      </x:c>
+      <x:c r="J104" t="str">
+        <x:v>Lecturer</x:v>
+      </x:c>
+      <x:c r="K104" t="str">
+        <x:v>Internship / Placement</x:v>
+      </x:c>
+      <x:c r="L104" t="str">
+        <x:v>Placement</x:v>
+      </x:c>
+      <x:c r="M104" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N104" t="str"/>
+      <x:c r="O104" t="str"/>
+      <x:c r="P104" t="str"/>
+      <x:c r="Q104" t="str"/>
+    </x:row>
+    <x:row r="105">
+      <x:c r="A105" t="str">
+        <x:v>PRPSTFPT55</x:v>
+      </x:c>
+      <x:c r="B105" t="str">
+        <x:v>Foc Dovs Lhr</x:v>
+      </x:c>
+      <x:c r="C105" t="str">
+        <x:v>Pending From Linkage Officer</x:v>
+      </x:c>
+      <x:c r="D105" t="str">
+        <x:v>23 July 2026</x:v>
+      </x:c>
+      <x:c r="E105" t="str">
+        <x:v>2026-07-23</x:v>
+      </x:c>
+      <x:c r="F105" t="str">
+        <x:v>Lahore Campus</x:v>
+      </x:c>
+      <x:c r="G105" t="str">
+        <x:v>Faculty of Allied Health Sciences</x:v>
+      </x:c>
+      <x:c r="H105" t="str">
+        <x:v>Department of Optometry &amp; Vision Science</x:v>
+      </x:c>
+      <x:c r="I105" t="str">
+        <x:v>Foc Dovs Lhr</x:v>
+      </x:c>
+      <x:c r="J105" t="str">
+        <x:v>Lecturer</x:v>
+      </x:c>
+      <x:c r="K105" t="str">
+        <x:v>Internship / Placement</x:v>
+      </x:c>
+      <x:c r="L105" t="str">
+        <x:v>Placement</x:v>
+      </x:c>
+      <x:c r="M105" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N105" t="str"/>
+      <x:c r="O105" t="str"/>
+      <x:c r="P105" t="str"/>
+      <x:c r="Q105" t="str"/>
+    </x:row>
+    <x:row r="106">
+      <x:c r="A106" t="str">
+        <x:v>PRPSTFPT55</x:v>
+      </x:c>
+      <x:c r="B106" t="str">
+        <x:v>Foc Dovs Lhr</x:v>
+      </x:c>
+      <x:c r="C106" t="str">
+        <x:v>Pending From Linkage Officer</x:v>
+      </x:c>
+      <x:c r="D106" t="str">
+        <x:v>23 July 2026</x:v>
+      </x:c>
+      <x:c r="E106" t="str">
+        <x:v>2026-07-23</x:v>
+      </x:c>
+      <x:c r="F106" t="str">
+        <x:v>Lahore Campus</x:v>
+      </x:c>
+      <x:c r="G106" t="str">
+        <x:v>Faculty of Allied Health Sciences</x:v>
+      </x:c>
+      <x:c r="H106" t="str">
+        <x:v>Department of Optometry &amp; Vision Science</x:v>
+      </x:c>
+      <x:c r="I106" t="str">
+        <x:v>Foc Dovs Lhr</x:v>
+      </x:c>
+      <x:c r="J106" t="str">
+        <x:v>Lecturer</x:v>
+      </x:c>
+      <x:c r="K106" t="str">
+        <x:v>Internship / Placement</x:v>
+      </x:c>
+      <x:c r="L106" t="str">
+        <x:v>Placement</x:v>
+      </x:c>
+      <x:c r="M106" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N106" t="str"/>
+      <x:c r="O106" t="str"/>
+      <x:c r="P106" t="str"/>
+      <x:c r="Q106" t="str"/>
+    </x:row>
+    <x:row r="107">
+      <x:c r="A107" t="str">
+        <x:v>PRPSTFPT55</x:v>
+      </x:c>
+      <x:c r="B107" t="str">
+        <x:v>Foc Dovs Lhr</x:v>
+      </x:c>
+      <x:c r="C107" t="str">
+        <x:v>Pending From Linkage Officer</x:v>
+      </x:c>
+      <x:c r="D107" t="str">
+        <x:v>23 July 2026</x:v>
+      </x:c>
+      <x:c r="E107" t="str">
+        <x:v>2026-07-23</x:v>
+      </x:c>
+      <x:c r="F107" t="str">
+        <x:v>Lahore Campus</x:v>
+      </x:c>
+      <x:c r="G107" t="str">
+        <x:v>Faculty of Allied Health Sciences</x:v>
+      </x:c>
+      <x:c r="H107" t="str">
+        <x:v>Department of Optometry &amp; Vision Science</x:v>
+      </x:c>
+      <x:c r="I107" t="str">
+        <x:v>Foc Dovs Lhr</x:v>
+      </x:c>
+      <x:c r="J107" t="str">
+        <x:v>Lecturer</x:v>
+      </x:c>
+      <x:c r="K107" t="str">
+        <x:v>Internship / Placement</x:v>
+      </x:c>
+      <x:c r="L107" t="str">
+        <x:v>Placement</x:v>
+      </x:c>
+      <x:c r="M107" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N107" t="str"/>
+      <x:c r="O107" t="str"/>
+      <x:c r="P107" t="str"/>
+      <x:c r="Q107" t="str"/>
+    </x:row>
+    <x:row r="108">
+      <x:c r="A108" t="str">
+        <x:v>PRPSTFPT55</x:v>
+      </x:c>
+      <x:c r="B108" t="str">
+        <x:v>Foc Dovs Lhr</x:v>
+      </x:c>
+      <x:c r="C108" t="str">
+        <x:v>Pending From Linkage Officer</x:v>
+      </x:c>
+      <x:c r="D108" t="str">
+        <x:v>23 July 2026</x:v>
+      </x:c>
+      <x:c r="E108" t="str">
+        <x:v>2026-07-23</x:v>
+      </x:c>
+      <x:c r="F108" t="str">
+        <x:v>Lahore Campus</x:v>
+      </x:c>
+      <x:c r="G108" t="str">
+        <x:v>Faculty of Allied Health Sciences</x:v>
+      </x:c>
+      <x:c r="H108" t="str">
+        <x:v>Department of Optometry &amp; Vision Science</x:v>
+      </x:c>
+      <x:c r="I108" t="str">
+        <x:v>Foc Dovs Lhr</x:v>
+      </x:c>
+      <x:c r="J108" t="str">
+        <x:v>Lecturer</x:v>
+      </x:c>
+      <x:c r="K108" t="str">
+        <x:v>Internship / Placement</x:v>
+      </x:c>
+      <x:c r="L108" t="str">
+        <x:v>Placement</x:v>
+      </x:c>
+      <x:c r="M108" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N108" t="str"/>
+      <x:c r="O108" t="str"/>
+      <x:c r="P108" t="str"/>
+      <x:c r="Q108" t="str"/>
+    </x:row>
+    <x:row r="109">
+      <x:c r="A109" t="str">
+        <x:v>PRPSTFPT55</x:v>
+      </x:c>
+      <x:c r="B109" t="str">
+        <x:v>Foc Dovs Lhr</x:v>
+      </x:c>
+      <x:c r="C109" t="str">
+        <x:v>Pending From Linkage Officer</x:v>
+      </x:c>
+      <x:c r="D109" t="str">
+        <x:v>23 July 2026</x:v>
+      </x:c>
+      <x:c r="E109" t="str">
+        <x:v>2026-07-23</x:v>
+      </x:c>
+      <x:c r="F109" t="str">
+        <x:v>Lahore Campus</x:v>
+      </x:c>
+      <x:c r="G109" t="str">
+        <x:v>Faculty of Allied Health Sciences</x:v>
+      </x:c>
+      <x:c r="H109" t="str">
+        <x:v>Department of Optometry &amp; Vision Science</x:v>
+      </x:c>
+      <x:c r="I109" t="str">
+        <x:v>Foc Dovs Lhr</x:v>
+      </x:c>
+      <x:c r="J109" t="str">
+        <x:v>Lecturer</x:v>
+      </x:c>
+      <x:c r="K109" t="str">
+        <x:v>Internship / Placement</x:v>
+      </x:c>
+      <x:c r="L109" t="str">
+        <x:v>Placement</x:v>
+      </x:c>
+      <x:c r="M109" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N109" t="str"/>
+      <x:c r="O109" t="str"/>
+      <x:c r="P109" t="str"/>
+      <x:c r="Q109" t="str"/>
+    </x:row>
+    <x:row r="110">
+      <x:c r="A110" t="str">
+        <x:v>PRPSTFPT55</x:v>
+      </x:c>
+      <x:c r="B110" t="str">
+        <x:v>Foc Dovs Lhr</x:v>
+      </x:c>
+      <x:c r="C110" t="str">
+        <x:v>Pending From Linkage Officer</x:v>
+      </x:c>
+      <x:c r="D110" t="str">
+        <x:v>23 July 2026</x:v>
+      </x:c>
+      <x:c r="E110" t="str">
+        <x:v>2026-07-23</x:v>
+      </x:c>
+      <x:c r="F110" t="str">
+        <x:v>Lahore Campus</x:v>
+      </x:c>
+      <x:c r="G110" t="str">
+        <x:v>Faculty of Allied Health Sciences</x:v>
+      </x:c>
+      <x:c r="H110" t="str">
+        <x:v>Department of Optometry &amp; Vision Science</x:v>
+      </x:c>
+      <x:c r="I110" t="str">
+        <x:v>Foc Dovs Lhr</x:v>
+      </x:c>
+      <x:c r="J110" t="str">
+        <x:v>Lecturer</x:v>
+      </x:c>
+      <x:c r="K110" t="str">
+        <x:v>Internship / Placement</x:v>
+      </x:c>
+      <x:c r="L110" t="str">
+        <x:v>Placement</x:v>
+      </x:c>
+      <x:c r="M110" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N110" t="str"/>
+      <x:c r="O110" t="str"/>
+      <x:c r="P110" t="str"/>
+      <x:c r="Q110" t="str"/>
+    </x:row>
+    <x:row r="111">
+      <x:c r="A111" t="str">
+        <x:v>PRPSTFPT55</x:v>
+      </x:c>
+      <x:c r="B111" t="str">
+        <x:v>Foc Dovs Lhr</x:v>
+      </x:c>
+      <x:c r="C111" t="str">
+        <x:v>Pending From Linkage Officer</x:v>
+      </x:c>
+      <x:c r="D111" t="str">
+        <x:v>23 July 2026</x:v>
+      </x:c>
+      <x:c r="E111" t="str">
+        <x:v>2026-07-23</x:v>
+      </x:c>
+      <x:c r="F111" t="str">
+        <x:v>Lahore Campus</x:v>
+      </x:c>
+      <x:c r="G111" t="str">
+        <x:v>Faculty of Allied Health Sciences</x:v>
+      </x:c>
+      <x:c r="H111" t="str">
+        <x:v>Department of Optometry &amp; Vision Science</x:v>
+      </x:c>
+      <x:c r="I111" t="str">
+        <x:v>Foc Dovs Lhr</x:v>
+      </x:c>
+      <x:c r="J111" t="str">
+        <x:v>Lecturer</x:v>
+      </x:c>
+      <x:c r="K111" t="str">
+        <x:v>Internship / Placement</x:v>
+      </x:c>
+      <x:c r="L111" t="str">
+        <x:v>Placement</x:v>
+      </x:c>
+      <x:c r="M111" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N111" t="str"/>
+      <x:c r="O111" t="str"/>
+      <x:c r="P111" t="str"/>
+      <x:c r="Q111" t="str"/>
+    </x:row>
+    <x:row r="112">
+      <x:c r="A112" t="str">
+        <x:v>PRPSTFPT55</x:v>
+      </x:c>
+      <x:c r="B112" t="str">
+        <x:v>Foc Dovs Lhr</x:v>
+      </x:c>
+      <x:c r="C112" t="str">
+        <x:v>Pending From Linkage Officer</x:v>
+      </x:c>
+      <x:c r="D112" t="str">
+        <x:v>23 July 2026</x:v>
+      </x:c>
+      <x:c r="E112" t="str">
+        <x:v>2026-07-23</x:v>
+      </x:c>
+      <x:c r="F112" t="str">
+        <x:v>Lahore Campus</x:v>
+      </x:c>
+      <x:c r="G112" t="str">
+        <x:v>Faculty of Allied Health Sciences</x:v>
+      </x:c>
+      <x:c r="H112" t="str">
+        <x:v>Department of Optometry &amp; Vision Science</x:v>
+      </x:c>
+      <x:c r="I112" t="str">
+        <x:v>Foc Dovs Lhr</x:v>
+      </x:c>
+      <x:c r="J112" t="str">
+        <x:v>Lecturer</x:v>
+      </x:c>
+      <x:c r="K112" t="str">
+        <x:v>Internship / Placement</x:v>
+      </x:c>
+      <x:c r="L112" t="str">
+        <x:v>Placement</x:v>
+      </x:c>
+      <x:c r="M112" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N112" t="str"/>
+      <x:c r="O112" t="str"/>
+      <x:c r="P112" t="str"/>
+      <x:c r="Q112" t="str"/>
+    </x:row>
+    <x:row r="113">
+      <x:c r="A113" t="str">
+        <x:v>PRPSTFPT34</x:v>
+      </x:c>
+      <x:c r="B113" t="str">
+        <x:v>Foc Dou Lhr</x:v>
+      </x:c>
+      <x:c r="C113" t="str">
+        <x:v>Pending From Linkage Officer</x:v>
+      </x:c>
+      <x:c r="D113" t="str">
+        <x:v>17 July 2026</x:v>
+      </x:c>
+      <x:c r="E113" t="str">
+        <x:v>2026-07-17</x:v>
+      </x:c>
+      <x:c r="F113" t="str">
+        <x:v>Lahore Campus</x:v>
+      </x:c>
+      <x:c r="G113" t="str">
+        <x:v>Faculty of Languages &amp; Literature</x:v>
+      </x:c>
+      <x:c r="H113" t="str">
+        <x:v>Department of Urdu</x:v>
+      </x:c>
+      <x:c r="I113" t="str">
+        <x:v>Foc Dou Lhr</x:v>
+      </x:c>
+      <x:c r="J113" t="str">
+        <x:v>Lecturer</x:v>
+      </x:c>
+      <x:c r="K113" t="str">
+        <x:v>Internship / Placement</x:v>
+      </x:c>
+      <x:c r="L113" t="str">
+        <x:v>Internship</x:v>
+      </x:c>
+      <x:c r="M113" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N113" t="str"/>
+      <x:c r="O113" t="str"/>
+      <x:c r="P113" t="str"/>
+      <x:c r="Q113" t="str"/>
+    </x:row>
+    <x:row r="114">
+      <x:c r="A114" t="str">
+        <x:v>PRPSTFPT34</x:v>
+      </x:c>
+      <x:c r="B114" t="str">
+        <x:v>Foc Dou Lhr</x:v>
+      </x:c>
+      <x:c r="C114" t="str">
+        <x:v>Pending From Linkage Officer</x:v>
+      </x:c>
+      <x:c r="D114" t="str">
+        <x:v>17 July 2026</x:v>
+      </x:c>
+      <x:c r="E114" t="str">
+        <x:v>2026-07-17</x:v>
+      </x:c>
+      <x:c r="F114" t="str">
+        <x:v>Lahore Campus</x:v>
+      </x:c>
+      <x:c r="G114" t="str">
+        <x:v>Faculty of Languages &amp; Literature</x:v>
+      </x:c>
+      <x:c r="H114" t="str">
+        <x:v>Department of Urdu</x:v>
+      </x:c>
+      <x:c r="I114" t="str">
+        <x:v>Foc Dou Lhr</x:v>
+      </x:c>
+      <x:c r="J114" t="str">
+        <x:v>Lecturer</x:v>
+      </x:c>
+      <x:c r="K114" t="str">
+        <x:v>Internship / Placement</x:v>
+      </x:c>
+      <x:c r="L114" t="str">
+        <x:v>Internship</x:v>
+      </x:c>
+      <x:c r="M114" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N114" t="str"/>
+      <x:c r="O114" t="str"/>
+      <x:c r="P114" t="str"/>
+      <x:c r="Q114" t="str"/>
+    </x:row>
+    <x:row r="115">
+      <x:c r="A115" t="str">
+        <x:v>PRPSTFPT28</x:v>
+      </x:c>
+      <x:c r="B115" t="str">
+        <x:v>Foc Doms Lhr</x:v>
+      </x:c>
+      <x:c r="C115" t="str">
+        <x:v>Pending From Linkage Officer</x:v>
+      </x:c>
+      <x:c r="D115" t="str">
+        <x:v>16 July 2026</x:v>
+      </x:c>
+      <x:c r="E115" t="str">
+        <x:v>2026-07-14</x:v>
+      </x:c>
+      <x:c r="F115" t="str">
+        <x:v>Lahore Campus</x:v>
+      </x:c>
+      <x:c r="G115" t="str">
+        <x:v>Faculty of Sciences</x:v>
+      </x:c>
+      <x:c r="H115" t="str">
+        <x:v>Department of Mathematics and Statistics</x:v>
+      </x:c>
+      <x:c r="I115" t="str">
+        <x:v>Foc Doms Lhr</x:v>
+      </x:c>
+      <x:c r="J115" t="str">
+        <x:v>Assistant Professor</x:v>
+      </x:c>
+      <x:c r="K115" t="str">
+        <x:v>Internship / Placement</x:v>
+      </x:c>
+      <x:c r="L115" t="str">
+        <x:v>Internship</x:v>
+      </x:c>
+      <x:c r="M115" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N115" t="str"/>
+      <x:c r="O115" t="str"/>
+      <x:c r="P115" t="str"/>
+      <x:c r="Q115" t="str"/>
+    </x:row>
+    <x:row r="116">
+      <x:c r="A116" t="str">
+        <x:v>PRPSTFPT21</x:v>
+      </x:c>
+      <x:c r="B116" t="str">
+        <x:v>Foc Dce Lhr</x:v>
+      </x:c>
+      <x:c r="C116" t="str">
+        <x:v>Pending From Linkage Officer</x:v>
+      </x:c>
+      <x:c r="D116" t="str">
+        <x:v>9 July 2026</x:v>
+      </x:c>
+      <x:c r="E116" t="str">
+        <x:v>2026-07-01</x:v>
+      </x:c>
+      <x:c r="F116" t="str">
+        <x:v>Lahore Campus</x:v>
+      </x:c>
+      <x:c r="G116" t="str">
+        <x:v>Faculty of Engineering &amp; Technology</x:v>
+      </x:c>
+      <x:c r="H116" t="str">
+        <x:v>Department of Civil Engineering</x:v>
+      </x:c>
+      <x:c r="I116" t="str">
+        <x:v>Foc Dce Lhr</x:v>
+      </x:c>
+      <x:c r="J116" t="str">
+        <x:v>Assistant Professor</x:v>
+      </x:c>
+      <x:c r="K116" t="str">
+        <x:v>Internship / Placement</x:v>
+      </x:c>
+      <x:c r="L116" t="str">
+        <x:v>Internship</x:v>
+      </x:c>
+      <x:c r="M116" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N116" t="str"/>
+      <x:c r="O116" t="str"/>
+      <x:c r="P116" t="str"/>
+      <x:c r="Q116" t="str"/>
+    </x:row>
+    <x:row r="117">
+      <x:c r="A117" t="str">
+        <x:v>PRPSTFPT13</x:v>
+      </x:c>
+      <x:c r="B117" t="str">
+        <x:v>Foc Law Lhr</x:v>
+      </x:c>
+      <x:c r="C117" t="str">
+        <x:v>Pending From Linkage Officer</x:v>
+      </x:c>
+      <x:c r="D117" t="str">
+        <x:v>9 July 2026</x:v>
+      </x:c>
+      <x:c r="E117" t="str">
+        <x:v>2026-07-09</x:v>
+      </x:c>
+      <x:c r="F117" t="str">
+        <x:v>Lahore Campus</x:v>
+      </x:c>
+      <x:c r="G117" t="str">
+        <x:v>Faculty of Law</x:v>
+      </x:c>
+      <x:c r="H117" t="str">
+        <x:v>M.A Raoof College of Law</x:v>
+      </x:c>
+      <x:c r="I117" t="str">
+        <x:v>Foc Law Lhr</x:v>
+      </x:c>
+      <x:c r="J117" t="str">
+        <x:v>Lecturer</x:v>
+      </x:c>
+      <x:c r="K117" t="str">
+        <x:v>Internship / Placement</x:v>
+      </x:c>
+      <x:c r="L117" t="str">
+        <x:v>Placement</x:v>
+      </x:c>
+      <x:c r="M117" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N117" t="str"/>
+      <x:c r="O117" t="str"/>
+      <x:c r="P117" t="str"/>
+      <x:c r="Q117" t="str"/>
+    </x:row>
+    <x:row r="118">
+      <x:c r="A118" t="str">
+        <x:v>PRPSTFPT13</x:v>
+      </x:c>
+      <x:c r="B118" t="str">
+        <x:v>Foc Law Lhr</x:v>
+      </x:c>
+      <x:c r="C118" t="str">
+        <x:v>Pending From Linkage Officer</x:v>
+      </x:c>
+      <x:c r="D118" t="str">
+        <x:v>9 July 2026</x:v>
+      </x:c>
+      <x:c r="E118" t="str">
+        <x:v>2026-07-09</x:v>
+      </x:c>
+      <x:c r="F118" t="str">
+        <x:v>Lahore Campus</x:v>
+      </x:c>
+      <x:c r="G118" t="str">
+        <x:v>Faculty of Law</x:v>
+      </x:c>
+      <x:c r="H118" t="str">
+        <x:v>M.A Raoof College of Law</x:v>
+      </x:c>
+      <x:c r="I118" t="str">
+        <x:v>Foc Law Lhr</x:v>
+      </x:c>
+      <x:c r="J118" t="str">
+        <x:v>Lecturer</x:v>
+      </x:c>
+      <x:c r="K118" t="str">
+        <x:v>Internship / Placement</x:v>
+      </x:c>
+      <x:c r="L118" t="str">
+        <x:v>Placement</x:v>
+      </x:c>
+      <x:c r="M118" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N118" t="str"/>
+      <x:c r="O118" t="str"/>
+      <x:c r="P118" t="str"/>
+      <x:c r="Q118" t="str"/>
+    </x:row>
+    <x:row r="119">
+      <x:c r="A119" t="str">
+        <x:v>PRPSTFPT13</x:v>
+      </x:c>
+      <x:c r="B119" t="str">
+        <x:v>Foc Law Lhr</x:v>
+      </x:c>
+      <x:c r="C119" t="str">
+        <x:v>Pending From Linkage Officer</x:v>
+      </x:c>
+      <x:c r="D119" t="str">
+        <x:v>9 July 2026</x:v>
+      </x:c>
+      <x:c r="E119" t="str">
+        <x:v>2026-07-09</x:v>
+      </x:c>
+      <x:c r="F119" t="str">
+        <x:v>Lahore Campus</x:v>
+      </x:c>
+      <x:c r="G119" t="str">
+        <x:v>Faculty of Law</x:v>
+      </x:c>
+      <x:c r="H119" t="str">
+        <x:v>M.A Raoof College of Law</x:v>
+      </x:c>
+      <x:c r="I119" t="str">
+        <x:v>Foc Law Lhr</x:v>
+      </x:c>
+      <x:c r="J119" t="str">
+        <x:v>Lecturer</x:v>
+      </x:c>
+      <x:c r="K119" t="str">
+        <x:v>Internship / Placement</x:v>
+      </x:c>
+      <x:c r="L119" t="str">
+        <x:v>Internship</x:v>
+      </x:c>
+      <x:c r="M119" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N119" t="str"/>
+      <x:c r="O119" t="str"/>
+      <x:c r="P119" t="str"/>
+      <x:c r="Q119" t="str"/>
+    </x:row>
+    <x:row r="120">
+      <x:c r="A120" t="str">
+        <x:v>PRPSTFPT6</x:v>
+      </x:c>
+      <x:c r="B120" t="str">
+        <x:v>Foc Lbs Lhr</x:v>
+      </x:c>
+      <x:c r="C120" t="str">
+        <x:v>Rejected</x:v>
+      </x:c>
+      <x:c r="D120" t="str">
+        <x:v>15 June 2026</x:v>
+      </x:c>
+      <x:c r="E120" t="str">
+        <x:v>2026-01-15</x:v>
+      </x:c>
+      <x:c r="F120" t="str"/>
+      <x:c r="G120" t="str">
+        <x:v>Faculty of Management Sciences</x:v>
+      </x:c>
+      <x:c r="H120" t="str">
+        <x:v>Lahore Business School</x:v>
+      </x:c>
+      <x:c r="I120" t="str">
+        <x:v>Foc Lbs Lhr</x:v>
+      </x:c>
+      <x:c r="J120" t="str">
+        <x:v>ASSISTAANT PROFESSOR</x:v>
+      </x:c>
+      <x:c r="K120" t="str">
+        <x:v>Internship / Placement</x:v>
+      </x:c>
+      <x:c r="L120" t="str">
+        <x:v>Placement</x:v>
+      </x:c>
+      <x:c r="M120" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N120" t="str"/>
+      <x:c r="O120" t="str"/>
+      <x:c r="P120" t="str"/>
+      <x:c r="Q120" t="str"/>
+    </x:row>
+    <x:row r="121">
+      <x:c r="A121" t="str">
+        <x:v>PRPSTFPT103</x:v>
+      </x:c>
+      <x:c r="B121" t="str">
+        <x:v>Foc Soca Lhr</x:v>
+      </x:c>
+      <x:c r="C121" t="str">
+        <x:v>Pending From Linkage Officer</x:v>
+      </x:c>
+      <x:c r="D121" t="str">
+        <x:v>7 October 2026</x:v>
+      </x:c>
+      <x:c r="E121" t="str"/>
+      <x:c r="F121" t="str">
+        <x:v>Lahore Campus</x:v>
+      </x:c>
+      <x:c r="G121" t="str">
+        <x:v>Faculty of Arts and Architecture</x:v>
+      </x:c>
+      <x:c r="H121" t="str">
+        <x:v>School of Creative Arts</x:v>
+      </x:c>
+      <x:c r="I121" t="str">
+        <x:v>Foc Soca Lhr</x:v>
+      </x:c>
+      <x:c r="J121" t="str"/>
+      <x:c r="K121" t="str">
+        <x:v>Internship / Placement</x:v>
+      </x:c>
+      <x:c r="L121" t="str">
+        <x:v>Internship/Placement</x:v>
+      </x:c>
+      <x:c r="M121" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N121" t="str"/>
+      <x:c r="O121" t="str"/>
+      <x:c r="P121" t="str"/>
+      <x:c r="Q121" t="str"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
